--- a/Financial Analysis/PLUG.xlsx
+++ b/Financial Analysis/PLUG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D09B9A2A-B8A8-4686-B3B2-79EFE3C5BD7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D75BDC1F-EBE8-407A-8581-458B4FFA9648}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{160E3FAB-17BC-4ADC-8722-2695A6B3C06F}"/>
   </bookViews>
@@ -1032,14 +1032,14 @@
         <v>1</v>
       </c>
       <c r="D3" s="4">
-        <v>2.37</v>
+        <v>4.1500000000000004</v>
       </c>
       <c r="E3" s="3">
-        <v>45927</v>
+        <v>45937</v>
       </c>
       <c r="F3" s="3">
         <f ca="1">TODAY()</f>
-        <v>45927</v>
+        <v>45937</v>
       </c>
       <c r="G3" s="3">
         <v>45972</v>
@@ -1063,7 +1063,7 @@
       </c>
       <c r="D5" s="5">
         <f>D3*D4</f>
-        <v>2736.8760000000002</v>
+        <v>4792.42</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="D9" s="5">
         <f>D5-D8</f>
-        <v>2230.5760000000005</v>
+        <v>4286.1200000000008</v>
       </c>
     </row>
   </sheetData>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="AP44" s="4">
         <f>Main!D3</f>
-        <v>2.37</v>
+        <v>4.1500000000000004</v>
       </c>
     </row>
     <row r="45" spans="2:156" x14ac:dyDescent="0.3">
@@ -6568,7 +6568,7 @@
       </c>
       <c r="AP45" s="11">
         <f>AP43/AP44-1</f>
-        <v>-0.84446381726903419</v>
+        <v>-0.91117572215123155</v>
       </c>
     </row>
     <row r="46" spans="2:156" x14ac:dyDescent="0.3">

--- a/Financial Analysis/PLUG.xlsx
+++ b/Financial Analysis/PLUG.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D75BDC1F-EBE8-407A-8581-458B4FFA9648}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43BF1416-CFC2-45F9-AF72-CD8A5D30DB16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{160E3FAB-17BC-4ADC-8722-2695A6B3C06F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{160E3FAB-17BC-4ADC-8722-2695A6B3C06F}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -1032,14 +1032,14 @@
         <v>1</v>
       </c>
       <c r="D3" s="4">
-        <v>4.1500000000000004</v>
+        <v>3.51</v>
       </c>
       <c r="E3" s="3">
-        <v>45937</v>
+        <v>45950</v>
       </c>
       <c r="F3" s="3">
         <f ca="1">TODAY()</f>
-        <v>45937</v>
+        <v>45950</v>
       </c>
       <c r="G3" s="3">
         <v>45972</v>
@@ -1063,7 +1063,7 @@
       </c>
       <c r="D5" s="5">
         <f>D3*D4</f>
-        <v>4792.42</v>
+        <v>4053.3479999999995</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="D9" s="5">
         <f>D5-D8</f>
-        <v>4286.1200000000008</v>
+        <v>3547.0479999999998</v>
       </c>
     </row>
   </sheetData>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="AP44" s="4">
         <f>Main!D3</f>
-        <v>4.1500000000000004</v>
+        <v>3.51</v>
       </c>
     </row>
     <row r="45" spans="2:156" x14ac:dyDescent="0.3">
@@ -6568,7 +6568,7 @@
       </c>
       <c r="AP45" s="11">
         <f>AP43/AP44-1</f>
-        <v>-0.91117572215123155</v>
+        <v>-0.89497984242951878</v>
       </c>
     </row>
     <row r="46" spans="2:156" x14ac:dyDescent="0.3">

--- a/Financial Analysis/PLUG.xlsx
+++ b/Financial Analysis/PLUG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1364A4CC-F419-4350-8DAD-6544C070B836}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{566B904E-2176-4F2C-ADFA-49B6383F8157}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{160E3FAB-17BC-4ADC-8722-2695A6B3C06F}"/>
   </bookViews>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="140">
   <si>
     <t>PLUG</t>
   </si>
@@ -486,7 +486,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="4">
+    <numFmt numFmtId="8" formatCode="&quot;£&quot;#,##0.00;[Red]\-&quot;£&quot;#,##0.00"/>
     <numFmt numFmtId="164" formatCode="[$$-409]#,##0.00"/>
     <numFmt numFmtId="165" formatCode="0.00\x"/>
     <numFmt numFmtId="166" formatCode="0.0\x"/>
@@ -564,7 +565,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -588,6 +589,7 @@
     <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1032,14 +1034,14 @@
         <v>1</v>
       </c>
       <c r="D3" s="4">
-        <v>2.46</v>
+        <v>1.87</v>
       </c>
       <c r="E3" s="3">
-        <v>45975</v>
+        <v>46076</v>
       </c>
       <c r="F3" s="3">
         <f ca="1">TODAY()</f>
-        <v>45975</v>
+        <v>46076</v>
       </c>
       <c r="G3" s="3">
         <v>46079</v>
@@ -1063,7 +1065,7 @@
       </c>
       <c r="D5" s="5">
         <f>D3*D4</f>
-        <v>3422.8440000000001</v>
+        <v>2601.9180000000001</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -1105,7 +1107,7 @@
       </c>
       <c r="D9" s="5">
         <f>D5-D8</f>
-        <v>3207.444</v>
+        <v>2386.518</v>
       </c>
     </row>
   </sheetData>
@@ -5292,47 +5294,47 @@
         <v>925.2</v>
       </c>
       <c r="AB34" s="5">
-        <f>1391.4</f>
+        <f t="shared" ref="AB34:AL34" si="59">1391.4</f>
         <v>1391.4</v>
       </c>
       <c r="AC34" s="5">
-        <f>1391.4</f>
+        <f t="shared" si="59"/>
         <v>1391.4</v>
       </c>
       <c r="AD34" s="5">
-        <f>1391.4</f>
+        <f t="shared" si="59"/>
         <v>1391.4</v>
       </c>
       <c r="AE34" s="5">
-        <f>1391.4</f>
+        <f t="shared" si="59"/>
         <v>1391.4</v>
       </c>
       <c r="AF34" s="5">
-        <f>1391.4</f>
+        <f t="shared" si="59"/>
         <v>1391.4</v>
       </c>
       <c r="AG34" s="5">
-        <f>1391.4</f>
+        <f t="shared" si="59"/>
         <v>1391.4</v>
       </c>
       <c r="AH34" s="5">
-        <f>1391.4</f>
+        <f t="shared" si="59"/>
         <v>1391.4</v>
       </c>
       <c r="AI34" s="5">
-        <f>1391.4</f>
+        <f t="shared" si="59"/>
         <v>1391.4</v>
       </c>
       <c r="AJ34" s="5">
-        <f>1391.4</f>
+        <f t="shared" si="59"/>
         <v>1391.4</v>
       </c>
       <c r="AK34" s="5">
-        <f>1391.4</f>
+        <f t="shared" si="59"/>
         <v>1391.4</v>
       </c>
       <c r="AL34" s="5">
-        <f>1391.4</f>
+        <f t="shared" si="59"/>
         <v>1391.4</v>
       </c>
     </row>
@@ -5341,127 +5343,127 @@
         <v>53</v>
       </c>
       <c r="G35" s="7">
-        <f t="shared" ref="G35:R35" si="59">G33/G34</f>
+        <f t="shared" ref="G35:R35" si="60">G33/G34</f>
         <v>-0.23487949067758068</v>
       </c>
       <c r="H35" s="7">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>-0.26875852660300137</v>
       </c>
       <c r="I35" s="7">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>-0.33014911463187324</v>
       </c>
       <c r="J35" s="7">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>-0.73033196907685338</v>
       </c>
       <c r="K35" s="7">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>-0.33617553433378805</v>
       </c>
       <c r="L35" s="7">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>-0.29797635288767615</v>
       </c>
       <c r="M35" s="7">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>-0.24592264678471576</v>
       </c>
       <c r="N35" s="7">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>-1.4440121054907049</v>
       </c>
       <c r="O35" s="7">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>-0.18269498284336455</v>
       </c>
       <c r="P35" s="7">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>-0.19821614132317286</v>
       </c>
       <c r="Q35" s="7">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>-0.26139140434095154</v>
       </c>
       <c r="R35" s="7">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>-0.18705728043696995</v>
       </c>
       <c r="T35" s="7">
-        <f t="shared" ref="T35:AB35" si="60">T33/T34</f>
+        <f t="shared" ref="T35:AB35" si="61">T33/T34</f>
         <v>-0.14438381082310139</v>
       </c>
       <c r="U35" s="7">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>-8.8676671214188235E-2</v>
       </c>
       <c r="V35" s="7">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>-9.7203274215552554E-2</v>
       </c>
       <c r="W35" s="7">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>-0.67758071850841306</v>
       </c>
       <c r="X35" s="7">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>-0.52307867212369263</v>
       </c>
       <c r="Y35" s="7">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>-0.82321509777171442</v>
       </c>
       <c r="Z35" s="7">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>-1.5561618917689859</v>
       </c>
       <c r="AA35" s="7">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>-2.2750756593169044</v>
       </c>
       <c r="AB35" s="7">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>-0.7545432657754777</v>
       </c>
       <c r="AC35" s="7">
-        <f t="shared" ref="AC35:AL35" si="61">AC33/AC34</f>
+        <f t="shared" ref="AC35:AL35" si="62">AC33/AC34</f>
         <v>-0.3627122930142303</v>
       </c>
       <c r="AD35" s="7">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>-0.24905923906856386</v>
       </c>
       <c r="AE35" s="7">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>-0.13615194318628704</v>
       </c>
       <c r="AF35" s="7">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>-8.9185394498615553E-2</v>
       </c>
       <c r="AG35" s="7">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>-4.8675075636096042E-2</v>
       </c>
       <c r="AH35" s="7">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>-1.1209804019067508E-2</v>
       </c>
       <c r="AI35" s="7">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>2.6404444558310307E-2</v>
       </c>
       <c r="AJ35" s="7">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>6.4489126304865363E-2</v>
       </c>
       <c r="AK35" s="7">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>0.10543264121741605</v>
       </c>
       <c r="AL35" s="7">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>0.15072335424313046</v>
       </c>
     </row>
@@ -5470,7 +5472,7 @@
         <v>55</v>
       </c>
       <c r="K37" s="10">
-        <f t="shared" ref="K37:K42" si="62">K3/G3-1</f>
+        <f t="shared" ref="K37:K42" si="63">K3/G3-1</f>
         <v>-0.62493135639758379</v>
       </c>
       <c r="L37" s="10">
@@ -5478,44 +5480,44 @@
         <v>-0.64493758668515955</v>
       </c>
       <c r="M37" s="10">
-        <f t="shared" ref="M37:N42" si="63">M3/I3-1</f>
+        <f t="shared" ref="M37:N42" si="64">M3/I3-1</f>
         <v>-0.26188835286009648</v>
       </c>
       <c r="N37" s="10">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>-0.17748659916616993</v>
       </c>
       <c r="O37" s="10">
-        <f t="shared" ref="O37:O42" si="64">O3/K3-1</f>
+        <f t="shared" ref="O37:O42" si="65">O3/K3-1</f>
         <v>-7.0278184480234263E-2</v>
       </c>
       <c r="P37" s="10">
-        <f t="shared" ref="P37:P42" si="65">P3/L3-1</f>
+        <f t="shared" ref="P37:P42" si="66">P3/L3-1</f>
         <v>0.29166666666666674</v>
       </c>
       <c r="Q37" s="10">
-        <f t="shared" ref="Q37:Q42" si="66">Q3/M3-1</f>
+        <f t="shared" ref="Q37:Q42" si="67">Q3/M3-1</f>
         <v>-9.6171802054154987E-2</v>
       </c>
       <c r="R37" s="10">
-        <f t="shared" ref="R37:R42" si="67">R3/N3-1</f>
+        <f t="shared" ref="R37:R42" si="68">R3/N3-1</f>
         <v>0.10000000000000009</v>
       </c>
       <c r="T37" s="10"/>
       <c r="U37" s="10">
-        <f t="shared" ref="U37:X42" si="68">U3/T3-1</f>
+        <f t="shared" ref="U37:X42" si="69">U3/T3-1</f>
         <v>0.71405750798722045</v>
       </c>
       <c r="V37" s="10">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>0.39701770736253494</v>
       </c>
       <c r="W37" s="10">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>-1.6290860573715809</v>
       </c>
       <c r="X37" s="10">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>-5.1654294803817606</v>
       </c>
       <c r="Y37" s="10">
@@ -5531,47 +5533,47 @@
         <v>-0.45136350857464147</v>
       </c>
       <c r="AB37" s="10">
-        <f t="shared" ref="AB37:AL42" si="69">AB3/AA3-1</f>
+        <f t="shared" ref="AB37:AL42" si="70">AB3/AA3-1</f>
         <v>5.4086600051242772E-2</v>
       </c>
       <c r="AC37" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>0.40000000000000013</v>
       </c>
       <c r="AD37" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="AE37" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>0.19999999999999996</v>
       </c>
       <c r="AF37" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AG37" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AH37" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AI37" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AJ37" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AK37" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AL37" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>0.10000000000000009</v>
       </c>
     </row>
@@ -5580,108 +5582,108 @@
         <v>56</v>
       </c>
       <c r="K38" s="10">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>0.4285714285714286</v>
       </c>
       <c r="L38" s="10">
-        <f t="shared" ref="L38:L42" si="70">L4/H4-1</f>
+        <f t="shared" ref="L38:L42" si="71">L4/H4-1</f>
         <v>0.49425287356321856</v>
       </c>
       <c r="M38" s="10">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>0.51612903225806428</v>
       </c>
       <c r="N38" s="10">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>8.3333333333333037E-3</v>
       </c>
       <c r="O38" s="10">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>0.29999999999999982</v>
       </c>
       <c r="P38" s="10">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>0.2615384615384615</v>
       </c>
       <c r="Q38" s="10">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>0.39716312056737579</v>
       </c>
       <c r="R38" s="10">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="T38" s="10"/>
       <c r="U38" s="10">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>0.35802469135802473</v>
       </c>
       <c r="V38" s="10">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>0.1454545454545455</v>
       </c>
       <c r="W38" s="10">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>-1.3888888888888888</v>
       </c>
       <c r="X38" s="10">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>-3.7244897959183669</v>
       </c>
       <c r="Y38" s="10">
-        <f t="shared" ref="Y38:Z42" si="71">Y4/X4-1</f>
+        <f t="shared" ref="Y38:Z42" si="72">Y4/X4-1</f>
         <v>0.32209737827715346</v>
       </c>
       <c r="Z38" s="10">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0.10764872521246471</v>
       </c>
       <c r="AA38" s="10">
-        <f t="shared" ref="AA38" si="72">AA4/Z4-1</f>
+        <f t="shared" ref="AA38" si="73">AA4/Z4-1</f>
         <v>0.3350383631713556</v>
       </c>
       <c r="AB38" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>0.38620689655172402</v>
       </c>
       <c r="AC38" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>0.39999999999999991</v>
       </c>
       <c r="AD38" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="AE38" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>0.19999999999999996</v>
       </c>
       <c r="AF38" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AG38" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AH38" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AI38" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AJ38" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AK38" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>9.9999999999999867E-2</v>
       </c>
       <c r="AL38" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AO38" t="s">
@@ -5696,115 +5698,115 @@
         <v>57</v>
       </c>
       <c r="K39" s="10">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>1.3164556962025316</v>
       </c>
       <c r="L39" s="10">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>0.22360248447204945</v>
       </c>
       <c r="M39" s="10">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>1.990049751243772E-2</v>
       </c>
       <c r="N39" s="10">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>-1.5306122448979997E-2</v>
       </c>
       <c r="O39" s="10">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>0.26775956284152991</v>
       </c>
       <c r="P39" s="10">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>0.19796954314720816</v>
       </c>
       <c r="Q39" s="10">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>0.20000000000000018</v>
       </c>
       <c r="R39" s="10">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="T39" s="10"/>
       <c r="U39" s="10">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>0.77519379844961223</v>
       </c>
       <c r="V39" s="10">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>0.13100436681222716</v>
       </c>
       <c r="W39" s="10">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>2.7027027027027195E-2</v>
       </c>
       <c r="X39" s="10">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>0.32330827067669166</v>
       </c>
       <c r="Y39" s="10">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0.34090909090909083</v>
       </c>
       <c r="Z39" s="10">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0.34957627118644075</v>
       </c>
       <c r="AA39" s="10">
-        <f t="shared" ref="AA39" si="73">AA5/Z5-1</f>
+        <f t="shared" ref="AA39" si="74">AA5/Z5-1</f>
         <v>0.22135007849293564</v>
       </c>
       <c r="AB39" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>0.24023136246786625</v>
       </c>
       <c r="AC39" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>0.14999999999999991</v>
       </c>
       <c r="AD39" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>0.12000000000000011</v>
       </c>
       <c r="AE39" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>9.000000000000008E-2</v>
       </c>
       <c r="AF39" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>8.0000000000000071E-2</v>
       </c>
       <c r="AG39" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>7.0000000000000062E-2</v>
       </c>
       <c r="AH39" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AI39" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AJ39" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AK39" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AL39" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AO39" t="s">
         <v>72</v>
       </c>
       <c r="AP39" s="10">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="40" spans="2:156" x14ac:dyDescent="0.3">
@@ -5812,108 +5814,108 @@
         <v>58</v>
       </c>
       <c r="K40" s="10">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>0.81188118811881194</v>
       </c>
       <c r="L40" s="10">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>0.67039106145251393</v>
       </c>
       <c r="M40" s="10">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>0.53608247422680422</v>
       </c>
       <c r="N40" s="10">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>5.8510638297872619E-2</v>
       </c>
       <c r="O40" s="10">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>0.61202185792349728</v>
       </c>
       <c r="P40" s="10">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>0.15050167224080258</v>
       </c>
       <c r="Q40" s="10">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>0.20469798657718119</v>
       </c>
       <c r="R40" s="10">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>1.0100502512562803</v>
       </c>
       <c r="T40" s="10"/>
       <c r="U40" s="10">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>1.7439024390243905</v>
       </c>
       <c r="V40" s="10">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>0.29333333333333345</v>
       </c>
       <c r="W40" s="10">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>-1.5532646048109966</v>
       </c>
       <c r="X40" s="10">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>-3.9130434782608692</v>
       </c>
       <c r="Y40" s="10">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0.21961620469083165</v>
       </c>
       <c r="Z40" s="10">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0.15734265734265729</v>
       </c>
       <c r="AA40" s="10">
-        <f t="shared" ref="AA40" si="74">AA6/Z6-1</f>
+        <f t="shared" ref="AA40" si="75">AA6/Z6-1</f>
         <v>0.47885196374622363</v>
       </c>
       <c r="AB40" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>0.42798774259448424</v>
       </c>
       <c r="AC40" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>0.25</v>
       </c>
       <c r="AD40" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>0.14999999999999991</v>
       </c>
       <c r="AE40" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>0.12000000000000011</v>
       </c>
       <c r="AF40" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>8.0000000000000071E-2</v>
       </c>
       <c r="AG40" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="AH40" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AI40" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AJ40" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AK40" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AL40" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AO40" t="s">
@@ -5921,7 +5923,7 @@
       </c>
       <c r="AP40" s="5">
         <f>NPV(AP39,AC33:EZ33)</f>
-        <v>-91.667694099013559</v>
+        <v>56.061271059394308</v>
       </c>
     </row>
     <row r="41" spans="2:156" x14ac:dyDescent="0.3">
@@ -5929,105 +5931,105 @@
         <v>59</v>
       </c>
       <c r="K41" s="10">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>1.4</v>
       </c>
       <c r="L41" s="10">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>2.3333333333333335</v>
       </c>
       <c r="M41" s="10">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>-0.55102040816326525</v>
       </c>
       <c r="N41" s="10">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>-0.45945945945945987</v>
       </c>
       <c r="O41" s="10">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>-0.75</v>
       </c>
       <c r="P41" s="10">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>-0.9</v>
       </c>
       <c r="Q41" s="10">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>-1</v>
       </c>
       <c r="R41" s="10">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>-0.49999999999999967</v>
       </c>
       <c r="T41" s="10"/>
       <c r="U41" s="10">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>-1</v>
       </c>
       <c r="V41" s="10"/>
       <c r="W41" s="10">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>0.49999999999999978</v>
       </c>
       <c r="X41" s="10">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>1.666666666666667</v>
       </c>
       <c r="Y41" s="10">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>2.4999999999999996</v>
       </c>
       <c r="Z41" s="10">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>2.8571428571428577</v>
       </c>
       <c r="AA41" s="10">
-        <f t="shared" ref="AA41" si="75">AA7/Z7-1</f>
+        <f t="shared" ref="AA41" si="76">AA7/Z7-1</f>
         <v>-1.8518518518518601E-2</v>
       </c>
       <c r="AB41" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>-0.81132075471698117</v>
       </c>
       <c r="AC41" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AD41" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AE41" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AF41" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AG41" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AH41" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AI41" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AJ41" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AK41" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AL41" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AO41" t="s">
@@ -6043,108 +6045,108 @@
         <v>60</v>
       </c>
       <c r="K42" s="11">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>-0.42768791627021885</v>
       </c>
       <c r="L42" s="11">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>-0.44888547271329737</v>
       </c>
       <c r="M42" s="11">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>-0.12625754527162991</v>
       </c>
       <c r="N42" s="11">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>-0.13783783783783754</v>
       </c>
       <c r="O42" s="11">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>0.1113881961762262</v>
       </c>
       <c r="P42" s="11">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>0.21338912133891208</v>
       </c>
       <c r="Q42" s="11">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>1.899827288428324E-2</v>
       </c>
       <c r="R42" s="11">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>0.24012539184952986</v>
       </c>
       <c r="T42" s="11"/>
       <c r="U42" s="11">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>0.74351297405189642</v>
       </c>
       <c r="V42" s="11">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>0.31825987406983369</v>
       </c>
       <c r="W42" s="11">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>-1.4051237516283108</v>
       </c>
       <c r="X42" s="11">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>-6.384780278670954</v>
       </c>
       <c r="Y42" s="11">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0.3960987261146498</v>
       </c>
       <c r="Z42" s="11">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0.27060165383518697</v>
       </c>
       <c r="AA42" s="11">
-        <f t="shared" ref="AA42" si="76">AA8/Z8-1</f>
+        <f t="shared" ref="AA42" si="77">AA8/Z8-1</f>
         <v>-0.29443447037701986</v>
       </c>
       <c r="AB42" s="11">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>0.14831424936386761</v>
       </c>
       <c r="AC42" s="11">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>0.33671924770794681</v>
       </c>
       <c r="AD42" s="11">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>0.25169256049188182</v>
       </c>
       <c r="AE42" s="11">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>0.1751766147126308</v>
       </c>
       <c r="AF42" s="11">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>9.492107442377451E-2</v>
       </c>
       <c r="AG42" s="11">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>8.7794263956019858E-2</v>
       </c>
       <c r="AH42" s="11">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>8.3411167928613583E-2</v>
       </c>
       <c r="AI42" s="11">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>8.2459549174470848E-2</v>
       </c>
       <c r="AJ42" s="11">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>8.341364059332701E-2</v>
       </c>
       <c r="AK42" s="11">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>8.4329303611484052E-2</v>
       </c>
       <c r="AL42" s="11">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>8.5206593911236972E-2</v>
       </c>
       <c r="AO42" t="s">
@@ -6152,7 +6154,7 @@
       </c>
       <c r="AP42" s="5">
         <f>AP40+AP41</f>
-        <v>123.73230590098642</v>
+        <v>271.46127105939428</v>
       </c>
     </row>
     <row r="43" spans="2:156" x14ac:dyDescent="0.3">
@@ -6160,19 +6162,19 @@
         <v>61</v>
       </c>
       <c r="G43" s="10">
-        <f t="shared" ref="G43:H43" si="77">(G3-G9)/G3</f>
+        <f t="shared" ref="G43:H43" si="78">(G3-G9)/G3</f>
         <v>0.13069741900054907</v>
       </c>
       <c r="H43" s="10">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>0.13361072584373557</v>
       </c>
       <c r="I43" s="10">
-        <f t="shared" ref="I43:J43" si="78">(I3-I9)/I3</f>
+        <f t="shared" ref="I43:J43" si="79">(I3-I9)/I3</f>
         <v>-9.5796002756719553E-2</v>
       </c>
       <c r="J43" s="10">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>-0.55390113162596855</v>
       </c>
       <c r="K43" s="10">
@@ -6184,47 +6186,47 @@
         <v>-0.69140625000000011</v>
       </c>
       <c r="M43" s="10">
-        <f t="shared" ref="M43:N43" si="79">(M3-M9)/M3</f>
+        <f t="shared" ref="M43:N43" si="80">(M3-M9)/M3</f>
         <v>-0.39962651727357623</v>
       </c>
       <c r="N43" s="10">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>-1.0362056480811006</v>
       </c>
       <c r="O43" s="10">
-        <f t="shared" ref="O43:R43" si="80">(O3-O9)/O3</f>
+        <f t="shared" ref="O43:R43" si="81">(O3-O9)/O3</f>
         <v>-0.17480314960629911</v>
       </c>
       <c r="P43" s="10">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>-0.18245967741935479</v>
       </c>
       <c r="Q43" s="10">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>-0.77169421487603307</v>
       </c>
       <c r="R43" s="10">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>-0.25000000000000011</v>
       </c>
       <c r="T43" s="10">
-        <f t="shared" ref="T43:X43" si="81">(T3-T9)/T3</f>
+        <f t="shared" ref="T43:X43" si="82">(T3-T9)/T3</f>
         <v>0.12460063897763585</v>
       </c>
       <c r="U43" s="10">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>0.21342031686859267</v>
       </c>
       <c r="V43" s="10">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>0.35356904603068712</v>
       </c>
       <c r="W43" s="10">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>2.8176033934252387</v>
       </c>
       <c r="X43" s="10">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>0.21792260692464363</v>
       </c>
       <c r="Y43" s="10">
@@ -6240,47 +6242,47 @@
         <v>-0.7834998718934153</v>
       </c>
       <c r="AB43" s="10">
-        <f t="shared" ref="AB43:AL43" si="82">(AB3-AB9)/AB3</f>
+        <f t="shared" ref="AB43:AL43" si="83">(AB3-AB9)/AB3</f>
         <v>-0.34485671228215159</v>
       </c>
       <c r="AC43" s="10">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>0.11999999999999995</v>
       </c>
       <c r="AD43" s="10">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>0.23999999999999996</v>
       </c>
       <c r="AE43" s="10">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>0.32</v>
       </c>
       <c r="AF43" s="10">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>0.33999999999999997</v>
       </c>
       <c r="AG43" s="10">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>0.35000000000000003</v>
       </c>
       <c r="AH43" s="10">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>0.36</v>
       </c>
       <c r="AI43" s="10">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>0.36</v>
       </c>
       <c r="AJ43" s="10">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>0.36000000000000004</v>
       </c>
       <c r="AK43" s="10">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>0.36</v>
       </c>
       <c r="AL43" s="10">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>0.36</v>
       </c>
       <c r="AO43" t="s">
@@ -6288,7 +6290,7 @@
       </c>
       <c r="AP43" s="4">
         <f>AP42/AL34</f>
-        <v>8.8926481170753496E-2</v>
+        <v>0.19509937549187456</v>
       </c>
     </row>
     <row r="44" spans="2:156" x14ac:dyDescent="0.3">
@@ -6296,19 +6298,19 @@
         <v>62</v>
       </c>
       <c r="G44" s="10">
-        <f t="shared" ref="G44:H44" si="83">(G4-G10-G11)/G4</f>
+        <f t="shared" ref="G44:H44" si="84">(G4-G10-G11)/G4</f>
         <v>-1.098901098901099</v>
       </c>
       <c r="H44" s="10">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>-2.5287356321839081</v>
       </c>
       <c r="I44" s="10">
-        <f t="shared" ref="I44:J44" si="84">(I4-I10-I11)/I4</f>
+        <f t="shared" ref="I44:J44" si="85">(I4-I10-I11)/I4</f>
         <v>-5.397849462365591</v>
       </c>
       <c r="J44" s="10">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>-3.3666666666666667</v>
       </c>
       <c r="K44" s="10">
@@ -6320,47 +6322,47 @@
         <v>-1.323076923076923</v>
       </c>
       <c r="M44" s="10">
-        <f t="shared" ref="M44:N44" si="85">(M4-M10-M11)/M4</f>
+        <f t="shared" ref="M44:N44" si="86">(M4-M10-M11)/M4</f>
         <v>-7.0921985815602842E-2</v>
       </c>
       <c r="N44" s="10">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>-1.6694214876033056</v>
       </c>
       <c r="O44" s="10">
-        <f t="shared" ref="O44:R44" si="86">(O4-O10-O11)/O4</f>
+        <f t="shared" ref="O44:R44" si="87">(O4-O10-O11)/O4</f>
         <v>-0.38461538461538475</v>
       </c>
       <c r="P44" s="10">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>1.0487804878048781</v>
       </c>
       <c r="Q44" s="10">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>0.19796954314720802</v>
       </c>
       <c r="R44" s="10">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>-0.65289256198347079</v>
       </c>
       <c r="T44" s="10">
-        <f t="shared" ref="T44:X44" si="87">(T4-T10-T11)/T4</f>
+        <f t="shared" ref="T44:X44" si="88">(T4-T10-T11)/T4</f>
         <v>-0.22222222222222232</v>
       </c>
       <c r="U44" s="10">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>-7.7272727272727243E-2</v>
       </c>
       <c r="V44" s="10">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>-0.1428571428571429</v>
       </c>
       <c r="W44" s="10">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>8.9591836734693864</v>
       </c>
       <c r="X44" s="10">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>-4.0823970037453181</v>
       </c>
       <c r="Y44" s="10">
@@ -6376,47 +6378,47 @@
         <v>-1.0363984674329501</v>
       </c>
       <c r="AB44" s="10">
-        <f t="shared" ref="AB44:AL44" si="88">(AB4-AB10-AB11)/AB4</f>
+        <f t="shared" ref="AB44:AL44" si="89">(AB4-AB10-AB11)/AB4</f>
         <v>2.7086788280818206E-2</v>
       </c>
       <c r="AC44" s="10">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>0.23569725775882497</v>
       </c>
       <c r="AD44" s="10">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>0.3584468682229876</v>
       </c>
       <c r="AE44" s="10">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>0.42142257196921379</v>
       </c>
       <c r="AF44" s="10">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>0.42376034338795532</v>
       </c>
       <c r="AG44" s="10">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>0.42720324311373836</v>
       </c>
       <c r="AH44" s="10">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>0.43278491388129575</v>
       </c>
       <c r="AI44" s="10">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>0.44024405572521325</v>
       </c>
       <c r="AJ44" s="10">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>0.44722852490633608</v>
       </c>
       <c r="AK44" s="10">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>0.45376852786684185</v>
       </c>
       <c r="AL44" s="10">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>0.45989234882077018</v>
       </c>
       <c r="AO44" t="s">
@@ -6424,7 +6426,7 @@
       </c>
       <c r="AP44" s="4">
         <f>Main!D3</f>
-        <v>2.46</v>
+        <v>1.87</v>
       </c>
     </row>
     <row r="45" spans="2:156" x14ac:dyDescent="0.3">
@@ -6432,19 +6434,19 @@
         <v>63</v>
       </c>
       <c r="G45" s="10">
-        <f t="shared" ref="G45:H45" si="89">(G5-G12)/G5</f>
+        <f t="shared" ref="G45:H45" si="90">(G5-G12)/G5</f>
         <v>-4.924050632911392</v>
       </c>
       <c r="H45" s="10">
-        <f t="shared" si="89"/>
+        <f t="shared" si="90"/>
         <v>-2.354037267080745</v>
       </c>
       <c r="I45" s="10">
-        <f t="shared" ref="I45:J45" si="90">(I5-I12)/I5</f>
+        <f t="shared" ref="I45:J45" si="91">(I5-I12)/I5</f>
         <v>-1.8358208955223878</v>
       </c>
       <c r="J45" s="10">
-        <f t="shared" si="90"/>
+        <f t="shared" si="91"/>
         <v>-2.1173469387755106</v>
       </c>
       <c r="K45" s="10">
@@ -6456,47 +6458,47 @@
         <v>-1.7563451776649743</v>
       </c>
       <c r="M45" s="10">
-        <f t="shared" ref="M45:N45" si="91">(M5-M12)/M5</f>
+        <f t="shared" ref="M45:N45" si="92">(M5-M12)/M5</f>
         <v>-1.5268292682926827</v>
       </c>
       <c r="N45" s="10">
-        <f t="shared" si="91"/>
+        <f t="shared" si="92"/>
         <v>-1.8808290155440435</v>
       </c>
       <c r="O45" s="10">
-        <f t="shared" ref="O45:R45" si="92">(O5-O12)/O5</f>
+        <f t="shared" ref="O45:R45" si="93">(O5-O12)/O5</f>
         <v>-1.1508620689655173</v>
       </c>
       <c r="P45" s="10">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>-0.91949152542372858</v>
       </c>
       <c r="Q45" s="10">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>-0.85365853658536583</v>
       </c>
       <c r="R45" s="10">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>-0.95296931048226441</v>
       </c>
       <c r="T45" s="10">
-        <f t="shared" ref="T45:X45" si="93">(T5-T12)/T5</f>
+        <f t="shared" ref="T45:X45" si="94">(T5-T12)/T5</f>
         <v>-1.4263565891472867</v>
       </c>
       <c r="U45" s="10">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>-0.58078602620087361</v>
       </c>
       <c r="V45" s="10">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>-0.54826254826254839</v>
       </c>
       <c r="W45" s="10">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>-1.4285714285714282</v>
       </c>
       <c r="X45" s="10">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>-1.9090909090909089</v>
       </c>
       <c r="Y45" s="10">
@@ -6512,47 +6514,47 @@
         <v>-1.7879177377892035</v>
       </c>
       <c r="AB45" s="10">
-        <f t="shared" ref="AB45:AL45" si="94">(AB5-AB12)/AB5</f>
+        <f t="shared" ref="AB45:AL45" si="95">(AB5-AB12)/AB5</f>
         <v>-0.96704321691366979</v>
       </c>
       <c r="AC45" s="10">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>-0.79999999999999993</v>
       </c>
       <c r="AD45" s="10">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>-0.50000000000000011</v>
       </c>
       <c r="AE45" s="10">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>-0.19999999999999993</v>
       </c>
       <c r="AF45" s="10">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>-0.10000000000000012</v>
       </c>
       <c r="AG45" s="10">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>-4.9999999999999975E-2</v>
       </c>
       <c r="AH45" s="10">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>0</v>
       </c>
       <c r="AI45" s="10">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>5.00000000000001E-2</v>
       </c>
       <c r="AJ45" s="10">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>6.999999999999991E-2</v>
       </c>
       <c r="AK45" s="10">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>7.9999999999999988E-2</v>
       </c>
       <c r="AL45" s="10">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>8.9999999999999969E-2</v>
       </c>
       <c r="AO45" s="1" t="s">
@@ -6560,7 +6562,7 @@
       </c>
       <c r="AP45" s="11">
         <f>AP43/AP44-1</f>
-        <v>-0.96385102391432786</v>
+        <v>-0.89566878315942533</v>
       </c>
     </row>
     <row r="46" spans="2:156" x14ac:dyDescent="0.3">
@@ -6568,127 +6570,127 @@
         <v>64</v>
       </c>
       <c r="G46" s="10">
-        <f t="shared" ref="G46:H46" si="95">(G6-G13)/G6</f>
+        <f t="shared" ref="G46:H46" si="96">(G6-G13)/G6</f>
         <v>-4.3960396039603964</v>
       </c>
       <c r="H46" s="10">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>-2.603351955307263</v>
       </c>
       <c r="I46" s="10">
-        <f t="shared" ref="I46:J46" si="96">(I6-I13)/I6</f>
+        <f t="shared" ref="I46:J46" si="97">(I6-I13)/I6</f>
         <v>-2.0412371134020622</v>
       </c>
       <c r="J46" s="10">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>-2.6329787234042552</v>
       </c>
       <c r="K46" s="10">
-        <f t="shared" ref="K46:L47" si="97">(K6-K13)/K6</f>
+        <f t="shared" ref="K46:L47" si="98">(K6-K13)/K6</f>
         <v>-2.2021857923497263</v>
       </c>
       <c r="L46" s="10">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>-0.94983277591973247</v>
       </c>
       <c r="M46" s="10">
-        <f t="shared" ref="M46:N46" si="98">(M6-M13)/M6</f>
+        <f t="shared" ref="M46:N46" si="99">(M6-M13)/M6</f>
         <v>-0.86241610738255026</v>
       </c>
       <c r="N46" s="10">
-        <f t="shared" si="98"/>
+        <f t="shared" si="99"/>
         <v>-1.834170854271356</v>
       </c>
       <c r="O46" s="10">
-        <f t="shared" ref="O46:R46" si="99">(O6-O13)/O6</f>
+        <f t="shared" ref="O46:R46" si="100">(O6-O13)/O6</f>
         <v>-1.0135593220338983</v>
       </c>
       <c r="P46" s="10">
-        <f t="shared" si="99"/>
+        <f t="shared" si="100"/>
         <v>-0.90697674418604646</v>
       </c>
       <c r="Q46" s="10">
-        <f t="shared" si="99"/>
+        <f t="shared" si="100"/>
         <v>-0.79387186629526485</v>
       </c>
       <c r="R46" s="10">
-        <f t="shared" si="99"/>
+        <f t="shared" si="100"/>
         <v>-0.82499999999999996</v>
       </c>
       <c r="T46" s="10">
-        <f t="shared" ref="T46:X46" si="100">(T6-T13)/T6</f>
+        <f t="shared" ref="T46:X46" si="101">(T6-T13)/T6</f>
         <v>-1.6829268292682928</v>
       </c>
       <c r="U46" s="10">
-        <f t="shared" si="100"/>
+        <f t="shared" si="101"/>
         <v>-0.23111111111111107</v>
       </c>
       <c r="V46" s="10">
-        <f t="shared" si="100"/>
+        <f t="shared" si="101"/>
         <v>-0.25085910652920951</v>
       </c>
       <c r="W46" s="10">
-        <f t="shared" si="100"/>
+        <f t="shared" si="101"/>
         <v>4.8385093167701863</v>
       </c>
       <c r="X46" s="10">
-        <f t="shared" si="100"/>
+        <f t="shared" si="101"/>
         <v>-1.7121535181236676</v>
       </c>
       <c r="Y46" s="10">
-        <f t="shared" ref="Y46:Z46" si="101">(Y6-Y13)/Y6</f>
+        <f t="shared" ref="Y46:Z46" si="102">(Y6-Y13)/Y6</f>
         <v>-2.3968531468531471</v>
       </c>
       <c r="Z46" s="10">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>-2.7205438066465257</v>
       </c>
       <c r="AA46" s="10">
-        <f t="shared" ref="AA46:AL46" si="102">(AA6-AA13)/AA6</f>
+        <f t="shared" ref="AA46:AL46" si="103">(AA6-AA13)/AA6</f>
         <v>-1.3370786516853932</v>
       </c>
       <c r="AB46" s="10">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>-0.87696709585121568</v>
       </c>
       <c r="AC46" s="10">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>-0.30000000000000004</v>
       </c>
       <c r="AD46" s="10">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>-0.14999999999999986</v>
       </c>
       <c r="AE46" s="10">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>-5.0000000000000072E-2</v>
       </c>
       <c r="AF46" s="10">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>0</v>
       </c>
       <c r="AG46" s="10">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>3.9999999999999987E-2</v>
       </c>
       <c r="AH46" s="10">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>2.9999999999999988E-2</v>
       </c>
       <c r="AI46" s="10">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>4.000000000000007E-2</v>
       </c>
       <c r="AJ46" s="10">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>5.0000000000000086E-2</v>
       </c>
       <c r="AK46" s="10">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>6.0000000000000026E-2</v>
       </c>
       <c r="AL46" s="10">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>7.0000000000000034E-2</v>
       </c>
       <c r="AO46" t="s">
@@ -6703,124 +6705,124 @@
         <v>65</v>
       </c>
       <c r="G47" s="10">
-        <f t="shared" ref="G47:H47" si="103">(G7-G14)/G7</f>
+        <f t="shared" ref="G47:H47" si="104">(G7-G14)/G7</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="H47" s="10">
-        <f t="shared" si="103"/>
+        <f t="shared" si="104"/>
         <v>-0.41666666666666669</v>
       </c>
       <c r="I47" s="10">
-        <f t="shared" ref="I47:J47" si="104">(I7-I14)/I7</f>
+        <f t="shared" ref="I47:J47" si="105">(I7-I14)/I7</f>
         <v>0.55102040816326525</v>
       </c>
       <c r="J47" s="10">
-        <f t="shared" si="104"/>
+        <f t="shared" si="105"/>
         <v>0.54054054054054068</v>
       </c>
       <c r="K47" s="10">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>0.29166666666666669</v>
       </c>
       <c r="L47" s="10">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>0.52500000000000002</v>
       </c>
       <c r="M47" s="10">
-        <f t="shared" ref="M47:N47" si="105">(M7-M14)/M7</f>
+        <f t="shared" ref="M47:N47" si="106">(M7-M14)/M7</f>
         <v>0.3636363636363637</v>
       </c>
       <c r="N47" s="10">
-        <f t="shared" si="105"/>
+        <f t="shared" si="106"/>
         <v>0.74999999999999989</v>
       </c>
       <c r="O47" s="10">
-        <f t="shared" ref="O47:R47" si="106">(O7-O14)/O7</f>
+        <f t="shared" ref="O47:R47" si="107">(O7-O14)/O7</f>
         <v>0.5</v>
       </c>
       <c r="P47" s="10">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>0.75000000000000011</v>
       </c>
       <c r="Q47" s="10" t="e">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R47" s="10">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>0.5</v>
       </c>
       <c r="T47" s="10">
-        <f t="shared" ref="T47:X47" si="107">(T7-T14)/T7</f>
+        <f t="shared" ref="T47:X47" si="108">(T7-T14)/T7</f>
         <v>0</v>
       </c>
       <c r="U47" s="10"/>
       <c r="V47" s="10">
-        <f t="shared" si="107"/>
+        <f t="shared" si="108"/>
         <v>0</v>
       </c>
       <c r="W47" s="10">
-        <f t="shared" si="107"/>
+        <f t="shared" si="108"/>
         <v>0</v>
       </c>
       <c r="X47" s="10">
-        <f t="shared" si="107"/>
+        <f t="shared" si="108"/>
         <v>-0.49999999999999989</v>
       </c>
       <c r="Y47" s="10">
-        <f t="shared" ref="Y47:Z47" si="108">(Y7-Y14)/Y7</f>
+        <f t="shared" ref="Y47:Z47" si="109">(Y7-Y14)/Y7</f>
         <v>7.1428571428571341E-2</v>
       </c>
       <c r="Z47" s="10">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>0.3981481481481482</v>
       </c>
       <c r="AA47" s="10">
-        <f t="shared" ref="AA47:AL47" si="109">(AA7-AA14)/AA7</f>
+        <f t="shared" ref="AA47:AL47" si="110">(AA7-AA14)/AA7</f>
         <v>0.48113207547169812</v>
       </c>
       <c r="AB47" s="10">
-        <f t="shared" si="109"/>
+        <f t="shared" si="110"/>
         <v>0.55000000000000004</v>
       </c>
       <c r="AC47" s="10">
-        <f t="shared" si="109"/>
+        <f t="shared" si="110"/>
         <v>0.5</v>
       </c>
       <c r="AD47" s="10">
-        <f t="shared" si="109"/>
+        <f t="shared" si="110"/>
         <v>0.5</v>
       </c>
       <c r="AE47" s="10">
-        <f t="shared" si="109"/>
+        <f t="shared" si="110"/>
         <v>0.5</v>
       </c>
       <c r="AF47" s="10">
-        <f t="shared" si="109"/>
+        <f t="shared" si="110"/>
         <v>0.5</v>
       </c>
       <c r="AG47" s="10">
-        <f t="shared" si="109"/>
+        <f t="shared" si="110"/>
         <v>0.5</v>
       </c>
       <c r="AH47" s="10">
-        <f t="shared" si="109"/>
+        <f t="shared" si="110"/>
         <v>0.5</v>
       </c>
       <c r="AI47" s="10">
-        <f t="shared" si="109"/>
+        <f t="shared" si="110"/>
         <v>0.5</v>
       </c>
       <c r="AJ47" s="10">
-        <f t="shared" si="109"/>
+        <f t="shared" si="110"/>
         <v>0.5</v>
       </c>
       <c r="AK47" s="10">
-        <f t="shared" si="109"/>
+        <f t="shared" si="110"/>
         <v>0.5</v>
       </c>
       <c r="AL47" s="10">
-        <f t="shared" si="109"/>
+        <f t="shared" si="110"/>
         <v>0.5</v>
       </c>
     </row>
@@ -6829,19 +6831,19 @@
         <v>68</v>
       </c>
       <c r="G48" s="11">
-        <f t="shared" ref="G48:H48" si="110">G16/G8</f>
+        <f t="shared" ref="G48:H48" si="111">G16/G8</f>
         <v>-0.33016175071360598</v>
       </c>
       <c r="H48" s="11">
-        <f t="shared" si="110"/>
+        <f t="shared" si="111"/>
         <v>-0.30015372790161426</v>
       </c>
       <c r="I48" s="11">
-        <f t="shared" ref="I48:J48" si="111">I16/I8</f>
+        <f t="shared" ref="I48:J48" si="112">I16/I8</f>
         <v>-0.69366197183098577</v>
       </c>
       <c r="J48" s="11">
-        <f t="shared" si="111"/>
+        <f t="shared" si="112"/>
         <v>-1.0018018018018027</v>
       </c>
       <c r="K48" s="11">
@@ -6853,47 +6855,47 @@
         <v>-0.91492329149232887</v>
       </c>
       <c r="M48" s="11">
-        <f t="shared" ref="M48:N48" si="112">M16/M8</f>
+        <f t="shared" ref="M48:N48" si="113">M16/M8</f>
         <v>-0.57570523891767422</v>
       </c>
       <c r="N48" s="11">
-        <f t="shared" si="112"/>
+        <f t="shared" si="113"/>
         <v>-1.2257053291536055</v>
       </c>
       <c r="O48" s="11">
-        <f t="shared" ref="O48:R48" si="113">O16/O8</f>
+        <f t="shared" ref="O48:R48" si="114">O16/O8</f>
         <v>-0.55272999252056843</v>
       </c>
       <c r="P48" s="11">
-        <f t="shared" si="113"/>
+        <f t="shared" si="114"/>
         <v>-0.30747126436781608</v>
       </c>
       <c r="Q48" s="11">
-        <f t="shared" si="113"/>
+        <f t="shared" si="114"/>
         <v>-0.67966101694915226</v>
       </c>
       <c r="R48" s="11">
-        <f t="shared" si="113"/>
+        <f t="shared" si="114"/>
         <v>-0.45090790360633631</v>
       </c>
       <c r="T48" s="11">
-        <f t="shared" ref="T48:X48" si="114">T16/T8</f>
+        <f t="shared" ref="T48:X48" si="115">T16/T8</f>
         <v>-0.27944111776447089</v>
       </c>
       <c r="U48" s="11">
-        <f t="shared" si="114"/>
+        <f t="shared" si="115"/>
         <v>1.5455065827132323E-2</v>
       </c>
       <c r="V48" s="11">
-        <f t="shared" si="114"/>
+        <f t="shared" si="115"/>
         <v>0.12114633087277456</v>
       </c>
       <c r="W48" s="11">
-        <f t="shared" si="114"/>
+        <f t="shared" si="115"/>
         <v>5.0310825294748129</v>
       </c>
       <c r="X48" s="11">
-        <f t="shared" si="114"/>
+        <f t="shared" si="115"/>
         <v>-0.34096337579617847</v>
       </c>
       <c r="Y48" s="11">
@@ -6909,47 +6911,47 @@
         <v>-0.99363867684478369</v>
       </c>
       <c r="AB48" s="11">
-        <f t="shared" ref="AB48:AL48" si="115">AB16/AB8</f>
+        <f t="shared" ref="AB48:AL48" si="116">AB16/AB8</f>
         <v>-0.49127150098329775</v>
       </c>
       <c r="AC48" s="11">
-        <f t="shared" si="115"/>
+        <f t="shared" si="116"/>
         <v>-4.8800517824701253E-2</v>
       </c>
       <c r="AD48" s="11">
-        <f t="shared" si="115"/>
+        <f t="shared" si="116"/>
         <v>0.11243530894726285</v>
       </c>
       <c r="AE48" s="11">
-        <f t="shared" si="115"/>
+        <f t="shared" si="116"/>
         <v>0.22335474511127673</v>
       </c>
       <c r="AF48" s="11">
-        <f t="shared" si="115"/>
+        <f t="shared" si="116"/>
         <v>0.2550916097090663</v>
       </c>
       <c r="AG48" s="11">
-        <f t="shared" si="115"/>
+        <f t="shared" si="116"/>
         <v>0.27564092057226092</v>
       </c>
       <c r="AH48" s="11">
-        <f t="shared" si="115"/>
+        <f t="shared" si="116"/>
         <v>0.28988059200603872</v>
       </c>
       <c r="AI48" s="11">
-        <f t="shared" si="115"/>
+        <f t="shared" si="116"/>
         <v>0.30073095105937264</v>
       </c>
       <c r="AJ48" s="11">
-        <f t="shared" si="115"/>
+        <f t="shared" si="116"/>
         <v>0.30836670333156718</v>
       </c>
       <c r="AK48" s="11">
-        <f t="shared" si="115"/>
+        <f t="shared" si="116"/>
         <v>0.31472729136595878</v>
       </c>
       <c r="AL48" s="11">
-        <f t="shared" si="115"/>
+        <f t="shared" si="116"/>
         <v>0.32068193497193831</v>
       </c>
     </row>
@@ -6970,100 +6972,100 @@
         <v>-0.35494880546075092</v>
       </c>
       <c r="M49" s="10">
-        <f t="shared" ref="M49:N49" si="116">M17/I17-1</f>
+        <f t="shared" ref="M49:N49" si="117">M17/I17-1</f>
         <v>-0.28880866425992779</v>
       </c>
       <c r="N49" s="10">
-        <f t="shared" si="116"/>
+        <f t="shared" si="117"/>
         <v>-0.5596026490066226</v>
       </c>
       <c r="O49" s="10">
-        <f t="shared" ref="O49:O50" si="117">O17/K17-1</f>
+        <f t="shared" ref="O49:O50" si="118">O17/K17-1</f>
         <v>-0.31225296442687756</v>
       </c>
       <c r="P49" s="10">
-        <f t="shared" ref="P49:P50" si="118">P17/L17-1</f>
+        <f t="shared" ref="P49:P50" si="119">P17/L17-1</f>
         <v>-0.35449735449735453</v>
       </c>
       <c r="Q49" s="10">
-        <f t="shared" ref="Q49:Q50" si="119">Q17/M17-1</f>
+        <f t="shared" ref="Q49:Q50" si="120">Q17/M17-1</f>
         <v>-0.18274111675126892</v>
       </c>
       <c r="R49" s="10">
-        <f t="shared" ref="R49:R50" si="120">R17/N17-1</f>
+        <f t="shared" ref="R49:R50" si="121">R17/N17-1</f>
         <v>0.10000000000000009</v>
       </c>
       <c r="T49" s="10"/>
       <c r="U49" s="10">
-        <f t="shared" ref="U49:U50" si="121">U17/T17-1</f>
+        <f t="shared" ref="U49:U50" si="122">U17/T17-1</f>
         <v>0.1811846689895471</v>
       </c>
       <c r="V49" s="10">
-        <f t="shared" ref="V49:V50" si="122">V17/U17-1</f>
+        <f t="shared" ref="V49:V50" si="123">V17/U17-1</f>
         <v>-5.8997050147491237E-3</v>
       </c>
       <c r="W49" s="10">
-        <f t="shared" ref="W49:W50" si="123">W17/V17-1</f>
+        <f t="shared" ref="W49:W50" si="124">W17/V17-1</f>
         <v>-0.17507418397626118</v>
       </c>
       <c r="X49" s="10">
-        <f t="shared" ref="X49:X50" si="124">X17/W17-1</f>
+        <f t="shared" ref="X49:X50" si="125">X17/W17-1</f>
         <v>1.3309352517985609</v>
       </c>
       <c r="Y49" s="10">
-        <f t="shared" ref="Y49:AA50" si="125">Y17/X17-1</f>
+        <f t="shared" ref="Y49:AA50" si="126">Y17/X17-1</f>
         <v>0.53703703703703698</v>
       </c>
       <c r="Z49" s="10">
-        <f t="shared" si="125"/>
+        <f t="shared" si="126"/>
         <v>0.14156626506024095</v>
       </c>
       <c r="AA49" s="10">
-        <f t="shared" si="125"/>
+        <f t="shared" si="126"/>
         <v>-0.32102022867194369</v>
       </c>
       <c r="AB49" s="10">
-        <f t="shared" ref="AB49:AB50" si="126">AB17/AA17-1</f>
+        <f t="shared" ref="AB49:AB50" si="127">AB17/AA17-1</f>
         <v>-0.21852331606217612</v>
       </c>
       <c r="AC49" s="10">
-        <f t="shared" ref="AC49:AC50" si="127">AC17/AB17-1</f>
+        <f t="shared" ref="AC49:AC50" si="128">AC17/AB17-1</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AD49" s="10">
-        <f t="shared" ref="AD49:AD50" si="128">AD17/AC17-1</f>
+        <f t="shared" ref="AD49:AD50" si="129">AD17/AC17-1</f>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="AE49" s="10">
-        <f t="shared" ref="AE49:AE50" si="129">AE17/AD17-1</f>
+        <f t="shared" ref="AE49:AE50" si="130">AE17/AD17-1</f>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AF49" s="10">
-        <f t="shared" ref="AF49:AF50" si="130">AF17/AE17-1</f>
+        <f t="shared" ref="AF49:AF50" si="131">AF17/AE17-1</f>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AG49" s="10">
-        <f t="shared" ref="AG49:AG50" si="131">AG17/AF17-1</f>
+        <f t="shared" ref="AG49:AG50" si="132">AG17/AF17-1</f>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AH49" s="10">
-        <f t="shared" ref="AH49:AH50" si="132">AH17/AG17-1</f>
+        <f t="shared" ref="AH49:AH50" si="133">AH17/AG17-1</f>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AI49" s="10">
-        <f t="shared" ref="AI49:AI50" si="133">AI17/AH17-1</f>
+        <f t="shared" ref="AI49:AI50" si="134">AI17/AH17-1</f>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AJ49" s="10">
-        <f t="shared" ref="AJ49:AJ50" si="134">AJ17/AI17-1</f>
+        <f t="shared" ref="AJ49:AJ50" si="135">AJ17/AI17-1</f>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AK49" s="10">
-        <f t="shared" ref="AK49:AK50" si="135">AK17/AJ17-1</f>
+        <f t="shared" ref="AK49:AK50" si="136">AK17/AJ17-1</f>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AL49" s="10">
-        <f t="shared" ref="AL49:AL50" si="136">AL17/AK17-1</f>
+        <f t="shared" ref="AL49:AL50" si="137">AL17/AK17-1</f>
         <v>3.0000000000000027E-2</v>
       </c>
     </row>
@@ -7084,100 +7086,100 @@
         <v>-0.15909090909090917</v>
       </c>
       <c r="M50" s="10">
-        <f t="shared" ref="M50:N50" si="137">M18/I18-1</f>
+        <f t="shared" ref="M50:N50" si="138">M18/I18-1</f>
         <v>-0.1317535545023697</v>
       </c>
       <c r="N50" s="10">
-        <f t="shared" si="137"/>
+        <f t="shared" si="138"/>
         <v>8.5867620751341578E-2</v>
       </c>
       <c r="O50" s="10">
-        <f t="shared" si="117"/>
+        <f t="shared" si="118"/>
         <v>3.589743589743577E-2</v>
       </c>
       <c r="P50" s="10">
-        <f t="shared" si="118"/>
+        <f t="shared" si="119"/>
         <v>3.2902467685076431E-2</v>
       </c>
       <c r="Q50" s="10">
-        <f t="shared" si="119"/>
+        <f t="shared" si="120"/>
         <v>0.2074235807860263</v>
       </c>
       <c r="R50" s="10">
-        <f t="shared" si="120"/>
+        <f t="shared" si="121"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="T50" s="10"/>
       <c r="U50" s="10">
-        <f t="shared" si="121"/>
+        <f t="shared" si="122"/>
         <v>-0.15111111111111108</v>
       </c>
       <c r="V50" s="10">
-        <f t="shared" si="122"/>
+        <f t="shared" si="123"/>
         <v>0.15968586387434547</v>
       </c>
       <c r="W50" s="10">
-        <f t="shared" si="123"/>
+        <f t="shared" si="124"/>
         <v>0.79006772009029347</v>
       </c>
       <c r="X50" s="10">
-        <f t="shared" si="124"/>
+        <f t="shared" si="125"/>
         <v>1.2686002522068098</v>
       </c>
       <c r="Y50" s="10">
-        <f t="shared" si="125"/>
+        <f t="shared" si="126"/>
         <v>1.0227904391328515</v>
       </c>
       <c r="Z50" s="10">
-        <f t="shared" si="125"/>
+        <f t="shared" si="126"/>
         <v>0.1610332508931025</v>
       </c>
       <c r="AA50" s="10">
-        <f t="shared" si="125"/>
+        <f t="shared" si="126"/>
         <v>-0.10982248520710058</v>
       </c>
       <c r="AB50" s="10">
-        <f t="shared" si="126"/>
+        <f t="shared" si="127"/>
         <v>6.8636001063546725E-2</v>
       </c>
       <c r="AC50" s="10">
-        <f t="shared" si="127"/>
+        <f t="shared" si="128"/>
         <v>-1.0000000000000009E-2</v>
       </c>
       <c r="AD50" s="10">
-        <f t="shared" si="128"/>
-        <v>1.0000000000000009E-2</v>
-      </c>
-      <c r="AE50" s="10">
         <f t="shared" si="129"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AF50" s="10">
+      <c r="AE50" s="10">
         <f t="shared" si="130"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AG50" s="10">
+      <c r="AF50" s="10">
         <f t="shared" si="131"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AH50" s="10">
+      <c r="AG50" s="10">
         <f t="shared" si="132"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AI50" s="10">
+      <c r="AH50" s="10">
         <f t="shared" si="133"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AJ50" s="10">
+      <c r="AI50" s="10">
         <f t="shared" si="134"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AK50" s="10">
+      <c r="AJ50" s="10">
         <f t="shared" si="135"/>
         <v>1.0000000000000009E-2</v>
       </c>
+      <c r="AK50" s="10">
+        <f t="shared" si="136"/>
+        <v>1.0000000000000009E-2</v>
+      </c>
       <c r="AL50" s="10">
-        <f t="shared" si="136"/>
+        <f t="shared" si="137"/>
         <v>1.0000000000000009E-2</v>
       </c>
     </row>
@@ -7186,19 +7188,19 @@
         <v>69</v>
       </c>
       <c r="G51" s="10">
-        <f t="shared" ref="G51:H51" si="138">G23/G8</f>
+        <f t="shared" ref="G51:H51" si="139">G23/G8</f>
         <v>-0.99809705042816366</v>
       </c>
       <c r="H51" s="10">
-        <f t="shared" si="138"/>
+        <f t="shared" si="139"/>
         <v>-0.8989239046887012</v>
       </c>
       <c r="I51" s="10">
-        <f t="shared" ref="I51:J51" si="139">I23/I8</f>
+        <f t="shared" ref="I51:J51" si="140">I23/I8</f>
         <v>-1.378269617706237</v>
       </c>
       <c r="J51" s="10">
-        <f t="shared" si="139"/>
+        <f t="shared" si="140"/>
         <v>-2.8189189189189205</v>
       </c>
       <c r="K51" s="10">
@@ -7210,47 +7212,47 @@
         <v>-1.7050209205020916</v>
       </c>
       <c r="M51" s="10">
-        <f t="shared" ref="M51:N51" si="140">M23/M8</f>
+        <f t="shared" ref="M51:N51" si="141">M23/M8</f>
         <v>-1.2440990213010938</v>
       </c>
       <c r="N51" s="10">
-        <f t="shared" si="140"/>
+        <f t="shared" si="141"/>
         <v>-6.7910135841170334</v>
       </c>
       <c r="O51" s="10">
-        <f t="shared" ref="O51:R51" si="141">O23/O8</f>
+        <f t="shared" ref="O51:R51" si="142">O23/O8</f>
         <v>-1.3358264771877335</v>
       </c>
       <c r="P51" s="10">
-        <f t="shared" si="141"/>
+        <f t="shared" si="142"/>
         <v>-1.0172413793103448</v>
       </c>
       <c r="Q51" s="10">
-        <f t="shared" si="141"/>
+        <f t="shared" si="142"/>
         <v>-1.971186440677966</v>
       </c>
       <c r="R51" s="10">
-        <f t="shared" si="141"/>
+        <f t="shared" si="142"/>
         <v>-1.0038401584091674</v>
       </c>
       <c r="T51" s="10">
-        <f t="shared" ref="T51:X51" si="142">T23/T8</f>
+        <f t="shared" ref="T51:X51" si="143">T23/T8</f>
         <v>-1.0149700598802394</v>
       </c>
       <c r="U51" s="10">
-        <f t="shared" si="142"/>
+        <f t="shared" si="143"/>
         <v>-0.39725243274184296</v>
       </c>
       <c r="V51" s="10">
-        <f t="shared" si="142"/>
+        <f t="shared" si="143"/>
         <v>-0.21754233608336962</v>
       </c>
       <c r="W51" s="10">
-        <f t="shared" si="142"/>
+        <f t="shared" si="143"/>
         <v>6.2604501607717049</v>
       </c>
       <c r="X51" s="10">
-        <f t="shared" si="142"/>
+        <f t="shared" si="143"/>
         <v>-0.87062101910828038</v>
       </c>
       <c r="Y51" s="10">
@@ -7266,47 +7268,47 @@
         <v>-3.2121501272264634</v>
       </c>
       <c r="AB51" s="10">
-        <f t="shared" ref="AB51:AL51" si="143">AB23/AB8</f>
+        <f t="shared" ref="AB51:AL51" si="144">AB23/AB8</f>
         <v>-1.3056691964656677</v>
       </c>
       <c r="AC51" s="10">
-        <f t="shared" si="143"/>
+        <f t="shared" si="144"/>
         <v>-0.52667600678207394</v>
       </c>
       <c r="AD51" s="10">
-        <f t="shared" si="143"/>
+        <f t="shared" si="144"/>
         <v>-0.27473897782363232</v>
       </c>
       <c r="AE51" s="10">
-        <f t="shared" si="143"/>
+        <f t="shared" si="144"/>
         <v>-0.11032842055055202</v>
       </c>
       <c r="AF51" s="10">
-        <f t="shared" si="143"/>
+        <f t="shared" si="144"/>
         <v>-5.3584419402333439E-2</v>
       </c>
       <c r="AG51" s="10">
-        <f t="shared" si="143"/>
+        <f t="shared" si="144"/>
         <v>-1.1786596051444193E-2</v>
       </c>
       <c r="AH51" s="10">
-        <f t="shared" si="143"/>
+        <f t="shared" si="144"/>
         <v>2.1143071266138822E-2</v>
       </c>
       <c r="AI51" s="10">
-        <f t="shared" si="143"/>
+        <f t="shared" si="144"/>
         <v>4.9234846285260134E-2</v>
       </c>
       <c r="AJ51" s="10">
-        <f t="shared" si="143"/>
+        <f t="shared" si="144"/>
         <v>7.3201396912806777E-2</v>
       </c>
       <c r="AK51" s="10">
-        <f t="shared" si="143"/>
+        <f t="shared" si="144"/>
         <v>9.500693511007792E-2</v>
       </c>
       <c r="AL51" s="10">
-        <f t="shared" si="143"/>
+        <f t="shared" si="144"/>
         <v>0.1155476009186637</v>
       </c>
     </row>
@@ -7315,19 +7317,19 @@
         <v>51</v>
       </c>
       <c r="G52" s="10">
-        <f t="shared" ref="G52:H52" si="144">G32/G31</f>
+        <f t="shared" ref="G52:H52" si="145">G32/G31</f>
         <v>6.2530062530062542E-3</v>
       </c>
       <c r="H52" s="10">
-        <f t="shared" si="144"/>
+        <f t="shared" si="145"/>
         <v>3.7926675094816682E-3</v>
       </c>
       <c r="I52" s="10">
-        <f t="shared" ref="I52:J52" si="145">I32/I31</f>
+        <f t="shared" ref="I52:J52" si="146">I32/I31</f>
         <v>1.6313779937521696E-2</v>
       </c>
       <c r="J52" s="10">
-        <f t="shared" si="145"/>
+        <f t="shared" si="146"/>
         <v>7.7772592938248574E-4</v>
       </c>
       <c r="K52" s="10">
@@ -7339,47 +7341,47 @@
         <v>1.5238095238095243E-3</v>
       </c>
       <c r="M52" s="10">
-        <f t="shared" ref="M52:N52" si="146">M32/M31</f>
+        <f t="shared" ref="M52:N52" si="147">M32/M31</f>
         <v>-4.7393364928909954E-4</v>
       </c>
       <c r="N52" s="10">
-        <f t="shared" si="146"/>
+        <f t="shared" si="147"/>
         <v>1.9423278051695803E-3</v>
       </c>
       <c r="O52" s="10">
-        <f t="shared" ref="O52:R52" si="147">O32/O31</f>
+        <f t="shared" ref="O52:R52" si="148">O32/O31</f>
         <v>0</v>
       </c>
       <c r="P52" s="10">
-        <f t="shared" si="147"/>
+        <f t="shared" si="148"/>
         <v>0</v>
       </c>
       <c r="Q52" s="10">
-        <f t="shared" si="147"/>
+        <f t="shared" si="148"/>
         <v>-2.7502750275027507E-4</v>
       </c>
       <c r="R52" s="10">
-        <f t="shared" si="147"/>
+        <f t="shared" si="148"/>
         <v>0</v>
       </c>
       <c r="T52" s="10">
-        <f t="shared" ref="T52:X52" si="148">T32/T31</f>
+        <f t="shared" ref="T52:X52" si="149">T32/T31</f>
         <v>0</v>
       </c>
       <c r="U52" s="10">
-        <f t="shared" si="148"/>
+        <f t="shared" si="149"/>
         <v>0.10550458715596332</v>
       </c>
       <c r="V52" s="10">
-        <f t="shared" si="148"/>
+        <f t="shared" si="149"/>
         <v>0</v>
       </c>
       <c r="W52" s="10">
-        <f t="shared" si="148"/>
+        <f t="shared" si="149"/>
         <v>4.9138481174218249E-2</v>
       </c>
       <c r="X52" s="10">
-        <f t="shared" si="148"/>
+        <f t="shared" si="149"/>
         <v>3.4012177199244167E-2</v>
       </c>
       <c r="Y52" s="10">
@@ -7395,47 +7397,47 @@
         <v>1.2810780034162082E-3</v>
       </c>
       <c r="AB52" s="10">
-        <f t="shared" ref="AB52:AL52" si="149">AB32/AB31</f>
+        <f t="shared" ref="AB52:AL52" si="150">AB32/AB31</f>
         <v>-9.5258825372950231E-5</v>
       </c>
       <c r="AC52" s="10">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>0.1</v>
       </c>
       <c r="AD52" s="10">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>0.1</v>
       </c>
       <c r="AE52" s="10">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>0.1</v>
       </c>
       <c r="AF52" s="10">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>0.1</v>
       </c>
       <c r="AG52" s="10">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>0.1</v>
       </c>
       <c r="AH52" s="10">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>0.1</v>
       </c>
       <c r="AI52" s="10">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>0.1</v>
       </c>
       <c r="AJ52" s="10">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>0.1</v>
       </c>
       <c r="AK52" s="10">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>0.1</v>
       </c>
       <c r="AL52" s="10">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>0.1</v>
       </c>
     </row>
@@ -7444,19 +7446,19 @@
         <v>70</v>
       </c>
       <c r="G53" s="10">
-        <f t="shared" ref="G53:H53" si="150">G33/G8</f>
+        <f t="shared" ref="G53:H53" si="151">G33/G8</f>
         <v>-0.9828734538534728</v>
       </c>
       <c r="H53" s="10">
-        <f t="shared" si="150"/>
+        <f t="shared" si="151"/>
         <v>-0.90853189853958516</v>
       </c>
       <c r="I53" s="10">
-        <f t="shared" ref="I53:J53" si="151">I33/I8</f>
+        <f t="shared" ref="I53:J53" si="152">I33/I8</f>
         <v>-1.4255533199195169</v>
       </c>
       <c r="J53" s="10">
-        <f t="shared" si="151"/>
+        <f t="shared" si="152"/>
         <v>-2.8936936936936952</v>
       </c>
       <c r="K53" s="10">
@@ -7468,47 +7470,47 @@
         <v>-1.827754532775453</v>
       </c>
       <c r="M53" s="10">
-        <f t="shared" ref="M53:N53" si="152">M33/M8</f>
+        <f t="shared" ref="M53:N53" si="153">M33/M8</f>
         <v>-1.2153137593552101</v>
       </c>
       <c r="N53" s="10">
-        <f t="shared" si="152"/>
+        <f t="shared" si="153"/>
         <v>-6.9801462904911187</v>
       </c>
       <c r="O53" s="10">
-        <f t="shared" ref="O53:R53" si="153">O33/O8</f>
+        <f t="shared" ref="O53:R53" si="154">O33/O8</f>
         <v>-1.4734480179506355</v>
       </c>
       <c r="P53" s="10">
-        <f t="shared" si="153"/>
+        <f t="shared" si="154"/>
         <v>-1.3155172413793104</v>
       </c>
       <c r="Q53" s="10">
-        <f t="shared" si="153"/>
+        <f t="shared" si="154"/>
         <v>-2.0548022598870057</v>
       </c>
       <c r="R53" s="10">
-        <f t="shared" si="153"/>
+        <f t="shared" si="154"/>
         <v>-1.0965263734411863</v>
       </c>
       <c r="T53" s="10">
-        <f t="shared" ref="T53:X53" si="154">T33/T8</f>
+        <f t="shared" ref="T53:X53" si="155">T33/T8</f>
         <v>-1.2674650698602792</v>
       </c>
       <c r="U53" s="10">
-        <f t="shared" si="154"/>
+        <f t="shared" si="155"/>
         <v>-0.44647967945048633</v>
       </c>
       <c r="V53" s="10">
-        <f t="shared" si="154"/>
+        <f t="shared" si="155"/>
         <v>-0.37125488493269665</v>
       </c>
       <c r="W53" s="10">
-        <f t="shared" si="154"/>
+        <f t="shared" si="155"/>
         <v>6.3879957127545568</v>
       </c>
       <c r="X53" s="10">
-        <f t="shared" si="154"/>
+        <f t="shared" si="155"/>
         <v>-0.91580414012738875</v>
       </c>
       <c r="Y53" s="10">
@@ -7524,47 +7526,47 @@
         <v>-3.3474872773536899</v>
       </c>
       <c r="AB53" s="10">
-        <f t="shared" ref="AB53:AL53" si="155">AB33/AB8</f>
+        <f t="shared" ref="AB53:AL53" si="156">AB33/AB8</f>
         <v>-1.4539948203750379</v>
       </c>
       <c r="AC53" s="10">
-        <f t="shared" si="155"/>
+        <f t="shared" si="156"/>
         <v>-0.52287850079492004</v>
       </c>
       <c r="AD53" s="10">
-        <f t="shared" si="155"/>
+        <f t="shared" si="156"/>
         <v>-0.28684249824161095</v>
       </c>
       <c r="AE53" s="10">
-        <f t="shared" si="155"/>
+        <f t="shared" si="156"/>
         <v>-0.13343247533541056</v>
       </c>
       <c r="AF53" s="10">
-        <f t="shared" si="155"/>
+        <f t="shared" si="156"/>
         <v>-7.9826781872896019E-2</v>
       </c>
       <c r="AG53" s="10">
-        <f t="shared" si="155"/>
+        <f t="shared" si="156"/>
         <v>-4.0051128221866669E-2</v>
       </c>
       <c r="AH53" s="10">
-        <f t="shared" si="155"/>
+        <f t="shared" si="156"/>
         <v>-8.5135919569157455E-3</v>
       </c>
       <c r="AI53" s="10">
-        <f t="shared" si="155"/>
+        <f t="shared" si="156"/>
         <v>1.8525936516811767E-2</v>
       </c>
       <c r="AJ53" s="10">
-        <f t="shared" si="155"/>
+        <f t="shared" si="156"/>
         <v>4.1763350144319179E-2</v>
       </c>
       <c r="AK53" s="10">
-        <f t="shared" si="155"/>
+        <f t="shared" si="156"/>
         <v>6.2968410095532334E-2</v>
       </c>
       <c r="AL53" s="10">
-        <f t="shared" si="155"/>
+        <f t="shared" si="156"/>
         <v>8.2949881148222063E-2</v>
       </c>
     </row>
@@ -7573,31 +7575,31 @@
         <v>74</v>
       </c>
       <c r="J55" s="9">
-        <f t="shared" ref="J55:P55" si="156">J56+J62+J70-J79-J80-J81-J87-J88-J89</f>
+        <f t="shared" ref="J55:P55" si="157">J56+J62+J70-J79-J80-J81-J87-J88-J89</f>
         <v>665.39999999999986</v>
       </c>
       <c r="K55" s="9">
-        <f t="shared" si="156"/>
+        <f t="shared" si="157"/>
         <v>671.39999999999986</v>
       </c>
       <c r="L55" s="9">
-        <f t="shared" si="156"/>
+        <f t="shared" si="157"/>
         <v>571.20000000000005</v>
       </c>
       <c r="M55" s="9">
-        <f t="shared" si="156"/>
+        <f t="shared" si="157"/>
         <v>518.40000000000009</v>
       </c>
       <c r="N55" s="9">
-        <f t="shared" si="156"/>
+        <f t="shared" si="157"/>
         <v>396.60000000000014</v>
       </c>
       <c r="O55" s="9">
-        <f t="shared" si="156"/>
+        <f t="shared" si="157"/>
         <v>514.69999999999982</v>
       </c>
       <c r="P55" s="9">
-        <f t="shared" si="156"/>
+        <f t="shared" si="157"/>
         <v>267.40000000000003</v>
       </c>
       <c r="X55" s="9">
@@ -7823,31 +7825,31 @@
         <v>97</v>
       </c>
       <c r="J61" s="9">
-        <f t="shared" ref="J61:P61" si="157">SUM(J56:J60)</f>
+        <f t="shared" ref="J61:P61" si="158">SUM(J56:J60)</f>
         <v>1787</v>
       </c>
       <c r="K61" s="9">
-        <f t="shared" si="157"/>
+        <f t="shared" si="158"/>
         <v>1766.6</v>
       </c>
       <c r="L61" s="9">
-        <f t="shared" si="157"/>
+        <f t="shared" si="158"/>
         <v>1672.5000000000002</v>
       </c>
       <c r="M61" s="9">
-        <f t="shared" si="157"/>
+        <f t="shared" si="158"/>
         <v>1634</v>
       </c>
       <c r="N61" s="9">
-        <f t="shared" si="157"/>
+        <f t="shared" si="158"/>
         <v>1477.3999999999999</v>
       </c>
       <c r="O61" s="9">
-        <f t="shared" si="157"/>
+        <f t="shared" si="158"/>
         <v>1534</v>
       </c>
       <c r="P61" s="9">
-        <f t="shared" si="157"/>
+        <f t="shared" si="158"/>
         <v>1329.8000000000002</v>
       </c>
       <c r="X61" s="9">
@@ -8231,31 +8233,31 @@
         <v>98</v>
       </c>
       <c r="J72" s="9">
-        <f t="shared" ref="J72:P72" si="158">SUM(J62:J71)</f>
+        <f t="shared" ref="J72:P72" si="159">SUM(J62:J71)</f>
         <v>3115.9000000000005</v>
       </c>
       <c r="K72" s="9">
-        <f t="shared" si="158"/>
+        <f t="shared" si="159"/>
         <v>3080.7</v>
       </c>
       <c r="L72" s="9">
-        <f t="shared" si="158"/>
+        <f t="shared" si="159"/>
         <v>3107.3</v>
       </c>
       <c r="M72" s="9">
-        <f t="shared" si="158"/>
+        <f t="shared" si="159"/>
         <v>3090.7000000000003</v>
       </c>
       <c r="N72" s="9">
-        <f t="shared" si="158"/>
+        <f t="shared" si="159"/>
         <v>2125.4</v>
       </c>
       <c r="O72" s="9">
-        <f t="shared" si="158"/>
+        <f t="shared" si="159"/>
         <v>2099.6</v>
       </c>
       <c r="P72" s="9">
-        <f t="shared" si="158"/>
+        <f t="shared" si="159"/>
         <v>2023.7</v>
       </c>
       <c r="X72" s="9">
@@ -8280,31 +8282,31 @@
         <v>104</v>
       </c>
       <c r="J73" s="12">
-        <f t="shared" ref="J73:P73" si="159">J61+J72</f>
+        <f t="shared" ref="J73:P73" si="160">J61+J72</f>
         <v>4902.9000000000005</v>
       </c>
       <c r="K73" s="12">
-        <f t="shared" si="159"/>
+        <f t="shared" si="160"/>
         <v>4847.2999999999993</v>
       </c>
       <c r="L73" s="12">
-        <f t="shared" si="159"/>
+        <f t="shared" si="160"/>
         <v>4779.8</v>
       </c>
       <c r="M73" s="12">
-        <f t="shared" si="159"/>
+        <f t="shared" si="160"/>
         <v>4724.7000000000007</v>
       </c>
       <c r="N73" s="12">
-        <f t="shared" si="159"/>
+        <f t="shared" si="160"/>
         <v>3602.8</v>
       </c>
       <c r="O73" s="12">
-        <f t="shared" si="159"/>
+        <f t="shared" si="160"/>
         <v>3633.6</v>
       </c>
       <c r="P73" s="12">
-        <f t="shared" si="159"/>
+        <f t="shared" si="160"/>
         <v>3353.5</v>
       </c>
       <c r="X73" s="12">
@@ -8666,31 +8668,31 @@
         <v>99</v>
       </c>
       <c r="J83" s="9">
-        <f t="shared" ref="J83:P83" si="160">SUM(J74:J82)</f>
+        <f t="shared" ref="J83:P83" si="161">SUM(J74:J82)</f>
         <v>964.6</v>
       </c>
       <c r="K83" s="9">
-        <f t="shared" si="160"/>
+        <f t="shared" si="161"/>
         <v>911.5</v>
       </c>
       <c r="L83" s="9">
-        <f t="shared" si="160"/>
+        <f t="shared" si="161"/>
         <v>809.5</v>
       </c>
       <c r="M83" s="9">
-        <f t="shared" si="160"/>
+        <f t="shared" si="161"/>
         <v>786.90000000000009</v>
       </c>
       <c r="N83" s="9">
-        <f t="shared" si="160"/>
+        <f t="shared" si="161"/>
         <v>748.5</v>
       </c>
       <c r="O83" s="9">
-        <f t="shared" si="160"/>
+        <f t="shared" si="161"/>
         <v>788.4</v>
       </c>
       <c r="P83" s="9">
-        <f t="shared" si="160"/>
+        <f t="shared" si="161"/>
         <v>835.80000000000007</v>
       </c>
       <c r="X83" s="9">
@@ -8981,31 +8983,31 @@
         <v>101</v>
       </c>
       <c r="J91" s="9">
-        <f t="shared" ref="J91:P91" si="161">SUM(J84:J90)</f>
+        <f t="shared" ref="J91:P91" si="162">SUM(J84:J90)</f>
         <v>1039.9000000000001</v>
       </c>
       <c r="K91" s="9">
-        <f t="shared" si="161"/>
+        <f t="shared" si="162"/>
         <v>1006.7</v>
       </c>
       <c r="L91" s="9">
-        <f t="shared" si="161"/>
+        <f t="shared" si="162"/>
         <v>981.7</v>
       </c>
       <c r="M91" s="9">
-        <f t="shared" si="161"/>
+        <f t="shared" si="162"/>
         <v>908.49999999999989</v>
       </c>
       <c r="N91" s="9">
-        <f t="shared" si="161"/>
+        <f t="shared" si="162"/>
         <v>1046.5</v>
       </c>
       <c r="O91" s="9">
-        <f t="shared" si="161"/>
+        <f t="shared" si="162"/>
         <v>912.5</v>
       </c>
       <c r="P91" s="9">
-        <f t="shared" si="161"/>
+        <f t="shared" si="162"/>
         <v>754</v>
       </c>
       <c r="X91" s="9">
@@ -9071,31 +9073,31 @@
         <v>96</v>
       </c>
       <c r="J93" s="12">
-        <f t="shared" ref="J93:P93" si="162">J83+J91+J92</f>
+        <f t="shared" ref="J93:P93" si="163">J83+J91+J92</f>
         <v>4902.6000000000004</v>
       </c>
       <c r="K93" s="12">
-        <f t="shared" si="162"/>
+        <f t="shared" si="163"/>
         <v>4847.2</v>
       </c>
       <c r="L93" s="12">
-        <f t="shared" si="162"/>
+        <f t="shared" si="163"/>
         <v>4779.8</v>
       </c>
       <c r="M93" s="12">
-        <f t="shared" si="162"/>
+        <f t="shared" si="163"/>
         <v>4724.7000000000007</v>
       </c>
       <c r="N93" s="12">
-        <f t="shared" si="162"/>
+        <f t="shared" si="163"/>
         <v>3602.8</v>
       </c>
       <c r="O93" s="12">
-        <f t="shared" si="162"/>
+        <f t="shared" si="163"/>
         <v>3633.5</v>
       </c>
       <c r="P93" s="12">
-        <f t="shared" si="162"/>
+        <f t="shared" si="163"/>
         <v>3353.8</v>
       </c>
       <c r="X93" s="12">
@@ -9128,27 +9130,27 @@
         <v>133</v>
       </c>
       <c r="J95" s="10">
-        <f t="shared" ref="J95:O95" si="163">J33/J92</f>
+        <f t="shared" ref="J95:O95" si="164">J33/J92</f>
         <v>-0.22166246851385399</v>
       </c>
       <c r="K95" s="10">
-        <f t="shared" si="163"/>
+        <f t="shared" si="164"/>
         <v>-0.10095595766473199</v>
       </c>
       <c r="L95" s="10">
-        <f t="shared" si="163"/>
+        <f t="shared" si="164"/>
         <v>-8.7699926386937022E-2</v>
       </c>
       <c r="M95" s="10">
-        <f t="shared" si="163"/>
+        <f t="shared" si="164"/>
         <v>-6.9686066087875087E-2</v>
       </c>
       <c r="N95" s="10">
-        <f t="shared" si="163"/>
+        <f t="shared" si="164"/>
         <v>-0.73901980307556159</v>
       </c>
       <c r="O95" s="10">
-        <f t="shared" si="163"/>
+        <f t="shared" si="164"/>
         <v>-0.10193521680637484</v>
       </c>
       <c r="P95" s="10">
@@ -9156,19 +9158,19 @@
         <v>-0.12976190476190477</v>
       </c>
       <c r="X95" s="10">
-        <f t="shared" ref="X95:Y95" si="164">X33/X92</f>
+        <f t="shared" ref="X95:Y95" si="165">X33/X92</f>
         <v>-9.9897952537073648E-2</v>
       </c>
       <c r="Y95" s="10">
-        <f t="shared" si="164"/>
+        <f t="shared" si="165"/>
         <v>-0.17834096842520075</v>
       </c>
       <c r="Z95" s="10">
-        <f t="shared" ref="Z95:AA95" si="165">Z33/Z92</f>
+        <f t="shared" ref="Z95:AA95" si="166">Z33/Z92</f>
         <v>-0.47230944411856046</v>
       </c>
       <c r="AA95" s="10">
-        <f t="shared" si="165"/>
+        <f t="shared" si="166"/>
         <v>-1.1643434008186746</v>
       </c>
     </row>
@@ -9177,27 +9179,27 @@
         <v>134</v>
       </c>
       <c r="J96" s="13">
-        <f t="shared" ref="J96:O96" si="166">J8/J73</f>
+        <f t="shared" ref="J96:O96" si="167">J8/J73</f>
         <v>4.5279324481429344E-2</v>
       </c>
       <c r="K96" s="13">
-        <f t="shared" si="166"/>
+        <f t="shared" si="167"/>
         <v>2.481793988405917E-2</v>
       </c>
       <c r="L96" s="13">
-        <f t="shared" si="166"/>
+        <f t="shared" si="167"/>
         <v>3.0001255282647809E-2</v>
       </c>
       <c r="M96" s="13">
-        <f t="shared" si="166"/>
+        <f t="shared" si="167"/>
         <v>3.6764238999301535E-2</v>
       </c>
       <c r="N96" s="13">
-        <f t="shared" si="166"/>
+        <f t="shared" si="167"/>
         <v>5.3125346952370381E-2</v>
       </c>
       <c r="O96" s="13">
-        <f t="shared" si="166"/>
+        <f t="shared" si="167"/>
         <v>3.6795464553060334E-2</v>
       </c>
       <c r="P96" s="13">
@@ -9205,19 +9207,19 @@
         <v>5.1886089160578498E-2</v>
       </c>
       <c r="X96" s="13">
-        <f t="shared" ref="X96:Y96" si="167">X8/X73</f>
+        <f t="shared" ref="X96:Y96" si="168">X8/X73</f>
         <v>8.4436974789915964E-2</v>
       </c>
       <c r="Y96" s="13">
-        <f t="shared" si="167"/>
+        <f t="shared" si="168"/>
         <v>0.12167999583644155</v>
       </c>
       <c r="Z96" s="13">
-        <f t="shared" ref="Z96:AA96" si="168">Z8/Z73</f>
+        <f t="shared" ref="Z96:AA96" si="169">Z8/Z73</f>
         <v>0.18176997287319749</v>
       </c>
       <c r="AA96" s="13">
-        <f t="shared" si="168"/>
+        <f t="shared" si="169"/>
         <v>0.17453092039524812</v>
       </c>
     </row>
@@ -9226,27 +9228,27 @@
         <v>135</v>
       </c>
       <c r="J97" s="13">
-        <f t="shared" ref="J97:O97" si="169">J73/J92</f>
+        <f t="shared" ref="J97:O97" si="170">J73/J92</f>
         <v>1.6917635692350164</v>
       </c>
       <c r="K97" s="13">
-        <f t="shared" si="169"/>
+        <f t="shared" si="170"/>
         <v>1.6549334243769203</v>
       </c>
       <c r="L97" s="13">
-        <f t="shared" si="169"/>
+        <f t="shared" si="170"/>
         <v>1.5993441745298804</v>
       </c>
       <c r="M97" s="13">
-        <f t="shared" si="169"/>
+        <f t="shared" si="170"/>
         <v>1.5596672498597037</v>
       </c>
       <c r="N97" s="13">
-        <f t="shared" si="169"/>
+        <f t="shared" si="170"/>
         <v>1.9929195707489769</v>
       </c>
       <c r="O97" s="13">
-        <f t="shared" si="169"/>
+        <f t="shared" si="170"/>
         <v>1.8801614405464142</v>
       </c>
       <c r="P97" s="13">
@@ -9254,19 +9256,19 @@
         <v>1.901077097505669</v>
       </c>
       <c r="X97" s="13">
-        <f t="shared" ref="X97:Y97" si="170">X73/X92</f>
+        <f t="shared" ref="X97:Y97" si="171">X73/X92</f>
         <v>1.2918774561955837</v>
       </c>
       <c r="Y97" s="13">
-        <f t="shared" si="170"/>
+        <f t="shared" si="171"/>
         <v>1.4197083887493225</v>
       </c>
       <c r="Z97" s="13">
-        <f t="shared" ref="Z97:AA97" si="171">Z73/Z92</f>
+        <f t="shared" ref="Z97:AA97" si="172">Z73/Z92</f>
         <v>1.6917635692350164</v>
       </c>
       <c r="AA97" s="13">
-        <f t="shared" si="171"/>
+        <f t="shared" si="172"/>
         <v>1.9929195707489769</v>
       </c>
     </row>
@@ -9275,39 +9277,39 @@
         <v>136</v>
       </c>
       <c r="J98" s="14">
-        <f t="shared" ref="J98:P98" si="172">J61/J83</f>
+        <f t="shared" ref="J98:P98" si="173">J61/J83</f>
         <v>1.8525813808832676</v>
       </c>
       <c r="K98" s="14">
-        <f t="shared" si="172"/>
+        <f t="shared" si="173"/>
         <v>1.9381239714755896</v>
       </c>
       <c r="L98" s="14">
-        <f t="shared" si="172"/>
+        <f t="shared" si="173"/>
         <v>2.0660901791229156</v>
       </c>
       <c r="M98" s="14">
-        <f t="shared" si="172"/>
+        <f t="shared" si="173"/>
         <v>2.0765027322404368</v>
       </c>
       <c r="N98" s="14">
-        <f t="shared" si="172"/>
+        <f t="shared" si="173"/>
         <v>1.9738142952571809</v>
       </c>
       <c r="O98" s="14">
-        <f t="shared" si="172"/>
+        <f t="shared" si="173"/>
         <v>1.945712836123795</v>
       </c>
       <c r="P98" s="14">
-        <f t="shared" si="172"/>
+        <f t="shared" si="173"/>
         <v>1.5910504905479781</v>
       </c>
       <c r="X98" s="14">
-        <f t="shared" ref="X98:Y98" si="173">X61/X83</f>
+        <f t="shared" ref="X98:Y98" si="174">X61/X83</f>
         <v>10.579310344827585</v>
       </c>
       <c r="Y98" s="14">
-        <f t="shared" si="173"/>
+        <f t="shared" si="174"/>
         <v>5.2035579345088161</v>
       </c>
       <c r="Z98" s="14">
@@ -9329,27 +9331,27 @@
         <v>137</v>
       </c>
       <c r="J99" s="14">
-        <f t="shared" ref="J99:O99" si="174">(J61-J58)/J83</f>
+        <f t="shared" ref="J99:O99" si="175">(J61-J58)/J83</f>
         <v>0.85600248807795976</v>
       </c>
       <c r="K99" s="14">
-        <f t="shared" si="174"/>
+        <f t="shared" si="175"/>
         <v>0.86747120131651112</v>
       </c>
       <c r="L99" s="14">
-        <f t="shared" si="174"/>
+        <f t="shared" si="175"/>
         <v>0.90549722050648573</v>
       </c>
       <c r="M99" s="14">
-        <f t="shared" si="174"/>
+        <f t="shared" si="175"/>
         <v>0.95081967213114749</v>
       </c>
       <c r="N99" s="14">
-        <f t="shared" si="174"/>
+        <f t="shared" si="175"/>
         <v>1.0618570474281894</v>
       </c>
       <c r="O99" s="14">
-        <f t="shared" si="174"/>
+        <f t="shared" si="175"/>
         <v>1.0660832064941654</v>
       </c>
       <c r="P99" s="14">
@@ -9357,11 +9359,11 @@
         <v>0.82065087341469267</v>
       </c>
       <c r="X99" s="14">
-        <f t="shared" ref="X99:Y99" si="175">(X61-X58)/X83</f>
+        <f t="shared" ref="X99:Y99" si="176">(X61-X58)/X83</f>
         <v>9.9391200951248511</v>
       </c>
       <c r="Y99" s="14">
-        <f t="shared" si="175"/>
+        <f t="shared" si="176"/>
         <v>4.1871851385390428</v>
       </c>
       <c r="Z99" s="14">
@@ -9387,35 +9389,35 @@
         <v>0.19585245505676135</v>
       </c>
       <c r="K100" s="10">
-        <f t="shared" ref="K100:P100" si="176">(SUM(K79:K81)+SUM(K87:K89))/K92</f>
+        <f t="shared" ref="K100:P100" si="177">(SUM(K79:K81)+SUM(K87:K89))/K92</f>
         <v>0.1923523386821441</v>
       </c>
       <c r="L100" s="10">
-        <f t="shared" si="176"/>
+        <f t="shared" si="177"/>
         <v>0.18222579134042696</v>
       </c>
       <c r="M100" s="10">
-        <f t="shared" si="176"/>
+        <f t="shared" si="177"/>
         <v>0.18964777341299968</v>
       </c>
       <c r="N100" s="10">
-        <f t="shared" si="176"/>
+        <f t="shared" si="177"/>
         <v>0.40358446730833059</v>
       </c>
       <c r="O100" s="10">
-        <f t="shared" si="176"/>
+        <f t="shared" si="177"/>
         <v>0.33478215874987066</v>
       </c>
       <c r="P100" s="10">
-        <f t="shared" si="176"/>
+        <f t="shared" si="177"/>
         <v>0.37159863945578231</v>
       </c>
       <c r="X100" s="10">
-        <f t="shared" ref="X100:Y100" si="177">(SUM(X79:X81)+SUM(X87:X89))/X92</f>
+        <f t="shared" ref="X100:Y100" si="178">(SUM(X79:X81)+SUM(X87:X89))/X92</f>
         <v>0.12469331480556702</v>
       </c>
       <c r="Y100" s="10">
-        <f t="shared" si="177"/>
+        <f t="shared" si="178"/>
         <v>0.13105265750455644</v>
       </c>
       <c r="Z100" s="10">
@@ -9423,7 +9425,7 @@
         <v>0.19585245505676135</v>
       </c>
       <c r="AA100" s="10">
-        <f t="shared" ref="AA100" si="178">(SUM(AA79:AA81)+SUM(AA87:AA89))/AA92</f>
+        <f t="shared" ref="AA100" si="179">(SUM(AA79:AA81)+SUM(AA87:AA89))/AA92</f>
         <v>0.40358446730833059</v>
       </c>
       <c r="AB100" s="10"/>
@@ -9441,43 +9443,43 @@
         <v>6.9385130373502477</v>
       </c>
       <c r="K101" s="14">
-        <f t="shared" ref="K101:P101" si="179">(K73-K83)/(SUM(K79:K81)+SUM(K87:K89))</f>
+        <f t="shared" ref="K101:P101" si="180">(K73-K83)/(SUM(K79:K81)+SUM(K87:K89))</f>
         <v>6.9858004969826029</v>
       </c>
       <c r="L101" s="14">
-        <f t="shared" si="179"/>
+        <f t="shared" si="180"/>
         <v>7.2903048108703636</v>
       </c>
       <c r="M101" s="14">
-        <f t="shared" si="179"/>
+        <f t="shared" si="180"/>
         <v>6.8543080939947796</v>
       </c>
       <c r="N101" s="14">
-        <f t="shared" si="179"/>
+        <f t="shared" si="180"/>
         <v>3.9121436403508771</v>
       </c>
       <c r="O101" s="14">
-        <f t="shared" si="179"/>
+        <f t="shared" si="180"/>
         <v>4.3975270479134467</v>
       </c>
       <c r="P101" s="14">
-        <f t="shared" si="179"/>
+        <f t="shared" si="180"/>
         <v>3.8408848207475206</v>
       </c>
       <c r="X101" s="14">
-        <f t="shared" ref="X101:Y101" si="180">(X73-X83)/(SUM(X79:X81)+SUM(X87:X89))</f>
+        <f t="shared" ref="X101:Y101" si="181">(X73-X83)/(SUM(X79:X81)+SUM(X87:X89))</f>
         <v>9.6282430785303852</v>
       </c>
       <c r="Y101" s="14">
-        <f t="shared" si="180"/>
+        <f t="shared" si="181"/>
         <v>9.6393535049802654</v>
       </c>
       <c r="Z101" s="14">
-        <f t="shared" ref="Z101:AA101" si="181">(Z73-Z83)/(SUM(Z79:Z81)+SUM(Z87:Z89))</f>
+        <f t="shared" ref="Z101:AA101" si="182">(Z73-Z83)/(SUM(Z79:Z81)+SUM(Z87:Z89))</f>
         <v>6.9385130373502477</v>
       </c>
       <c r="AA101" s="14">
-        <f t="shared" si="181"/>
+        <f t="shared" si="182"/>
         <v>3.9121436403508771</v>
       </c>
       <c r="AB101" s="14"/>
@@ -9499,27 +9501,27 @@
         <v>52</v>
       </c>
       <c r="G104" s="9">
-        <f t="shared" ref="G104" si="182">G33</f>
+        <f t="shared" ref="G104" si="183">G33</f>
         <v>-206.59999999999997</v>
       </c>
       <c r="H104" s="9">
-        <f t="shared" ref="H104:L104" si="183">H33</f>
+        <f t="shared" ref="H104:L104" si="184">H33</f>
         <v>-236.40000000000003</v>
       </c>
       <c r="I104" s="9">
-        <f t="shared" si="183"/>
+        <f t="shared" si="184"/>
         <v>-283.39999999999998</v>
       </c>
       <c r="J104" s="9">
-        <f t="shared" si="183"/>
+        <f t="shared" si="184"/>
         <v>-642.4000000000002</v>
       </c>
       <c r="K104" s="9">
-        <f t="shared" si="183"/>
+        <f t="shared" si="184"/>
         <v>-295.7</v>
       </c>
       <c r="L104" s="9">
-        <f t="shared" si="183"/>
+        <f t="shared" si="184"/>
         <v>-262.09999999999997</v>
       </c>
       <c r="M104" s="9">
@@ -9535,83 +9537,83 @@
         <v>-197</v>
       </c>
       <c r="P104" s="9">
-        <f t="shared" ref="P104:R104" si="184">P33</f>
+        <f t="shared" ref="P104:R104" si="185">P33</f>
         <v>-228.9</v>
       </c>
       <c r="Q104" s="9">
-        <f t="shared" si="184"/>
+        <f t="shared" si="185"/>
         <v>-363.7</v>
       </c>
       <c r="R104" s="9">
-        <f t="shared" si="184"/>
+        <f t="shared" si="185"/>
         <v>-260.2715</v>
       </c>
       <c r="V104" s="9">
-        <f t="shared" ref="V104:AB104" si="185">V33</f>
+        <f t="shared" ref="V104:AB104" si="186">V33</f>
         <v>-85.500000000000028</v>
       </c>
       <c r="W104" s="9">
-        <f t="shared" si="185"/>
+        <f t="shared" si="186"/>
         <v>-596.00000000000011</v>
       </c>
       <c r="X104" s="9">
-        <f t="shared" si="185"/>
+        <f t="shared" si="186"/>
         <v>-460.10000000000008</v>
       </c>
       <c r="Y104" s="9">
-        <f t="shared" si="185"/>
+        <f t="shared" si="186"/>
         <v>-724.1</v>
       </c>
       <c r="Z104" s="9">
-        <f t="shared" si="185"/>
+        <f t="shared" si="186"/>
         <v>-1368.8</v>
       </c>
       <c r="AA104" s="9">
-        <f t="shared" si="185"/>
+        <f t="shared" si="186"/>
         <v>-2104.9</v>
       </c>
       <c r="AB104" s="9">
-        <f t="shared" si="185"/>
+        <f t="shared" si="186"/>
         <v>-1049.8714999999997</v>
       </c>
       <c r="AC104" s="9">
-        <f t="shared" ref="AC104:AL104" si="186">AC33</f>
+        <f t="shared" ref="AC104:AL104" si="187">AC33</f>
         <v>-504.67788450000006</v>
       </c>
       <c r="AD104" s="9">
-        <f t="shared" si="186"/>
+        <f t="shared" si="187"/>
         <v>-346.54102523999978</v>
       </c>
       <c r="AE104" s="9">
-        <f t="shared" si="186"/>
+        <f t="shared" si="187"/>
         <v>-189.44181374939978</v>
       </c>
       <c r="AF104" s="9">
-        <f t="shared" si="186"/>
+        <f t="shared" si="187"/>
         <v>-124.09255790537368</v>
       </c>
       <c r="AG104" s="9">
-        <f t="shared" si="186"/>
+        <f t="shared" si="187"/>
         <v>-67.726500240064041</v>
       </c>
       <c r="AH104" s="9">
-        <f t="shared" si="186"/>
+        <f t="shared" si="187"/>
         <v>-15.597321312130532</v>
       </c>
       <c r="AI104" s="9">
-        <f t="shared" si="186"/>
+        <f t="shared" si="187"/>
         <v>36.739144158432964</v>
       </c>
       <c r="AJ104" s="9">
-        <f t="shared" si="186"/>
+        <f t="shared" si="187"/>
         <v>89.730170340589666</v>
       </c>
       <c r="AK104" s="9">
-        <f t="shared" si="186"/>
+        <f t="shared" si="187"/>
         <v>146.69897698991269</v>
       </c>
       <c r="AL104" s="9">
-        <f t="shared" si="186"/>
+        <f t="shared" si="187"/>
         <v>209.71647509389175</v>
       </c>
     </row>
@@ -9681,47 +9683,47 @@
         <v>61.1</v>
       </c>
       <c r="AB105" s="5">
-        <f t="shared" ref="AB105:AB132" si="187">SUM(O105:R105)</f>
+        <f t="shared" ref="AB105:AB132" si="188">SUM(O105:R105)</f>
         <v>53.9</v>
       </c>
       <c r="AC105" s="5">
-        <f t="shared" ref="AC105:AL106" si="188">AB105*1.05</f>
+        <f t="shared" ref="AC105:AL106" si="189">AB105*1.05</f>
         <v>56.594999999999999</v>
       </c>
       <c r="AD105" s="5">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>59.424750000000003</v>
       </c>
       <c r="AE105" s="5">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>62.395987500000004</v>
       </c>
       <c r="AF105" s="5">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>65.515786875000003</v>
       </c>
       <c r="AG105" s="5">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>68.791576218750009</v>
       </c>
       <c r="AH105" s="5">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>72.231155029687514</v>
       </c>
       <c r="AI105" s="5">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>75.842712781171898</v>
       </c>
       <c r="AJ105" s="5">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>79.634848420230497</v>
       </c>
       <c r="AK105" s="5">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>83.616590841242029</v>
       </c>
       <c r="AL105" s="5">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>87.797420383304129</v>
       </c>
     </row>
@@ -9756,7 +9758,7 @@
         <v>4.8</v>
       </c>
       <c r="N106" s="5">
-        <f t="shared" ref="N106:N135" si="189">AA106-M106-L106-K106</f>
+        <f t="shared" ref="N106:N135" si="190">AA106-M106-L106-K106</f>
         <v>9.1999999999999993</v>
       </c>
       <c r="O106" s="5">
@@ -9791,7 +9793,7 @@
         <v>23.4</v>
       </c>
       <c r="AB106" s="5">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>11</v>
       </c>
       <c r="AC106" s="5">
@@ -9799,39 +9801,39 @@
         <v>11.55</v>
       </c>
       <c r="AD106" s="5">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>12.127500000000001</v>
       </c>
       <c r="AE106" s="5">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>12.733875000000001</v>
       </c>
       <c r="AF106" s="5">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>13.370568750000002</v>
       </c>
       <c r="AG106" s="5">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>14.039097187500003</v>
       </c>
       <c r="AH106" s="5">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>14.741052046875003</v>
       </c>
       <c r="AI106" s="5">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>15.478104649218754</v>
       </c>
       <c r="AJ106" s="5">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>16.25200988167969</v>
       </c>
       <c r="AK106" s="5">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>17.064610375763674</v>
       </c>
       <c r="AL106" s="5">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>17.917840894551858</v>
       </c>
     </row>
@@ -9866,7 +9868,7 @@
         <v>14.399999999999999</v>
       </c>
       <c r="N107" s="5">
-        <f t="shared" si="189"/>
+        <f t="shared" si="190"/>
         <v>104.2</v>
       </c>
       <c r="O107" s="5">
@@ -9893,7 +9895,7 @@
         <v>172</v>
       </c>
       <c r="AB107" s="5">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>41.2</v>
       </c>
       <c r="AC107" s="5">
@@ -9958,7 +9960,7 @@
         <v>24.099999999999998</v>
       </c>
       <c r="N108" s="5">
-        <f t="shared" si="189"/>
+        <f t="shared" si="190"/>
         <v>18.100000000000009</v>
       </c>
       <c r="O108" s="5">
@@ -9993,7 +9995,7 @@
         <v>82.2</v>
       </c>
       <c r="AB108" s="5">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>55.2</v>
       </c>
       <c r="AC108" s="5">
@@ -10001,39 +10003,39 @@
         <v>56.856000000000002</v>
       </c>
       <c r="AD108" s="5">
-        <f t="shared" ref="AD108:AL108" si="190">AC108*1.03</f>
+        <f t="shared" ref="AD108:AL108" si="191">AC108*1.03</f>
         <v>58.561680000000003</v>
       </c>
       <c r="AE108" s="5">
-        <f t="shared" si="190"/>
+        <f t="shared" si="191"/>
         <v>60.318530400000007</v>
       </c>
       <c r="AF108" s="5">
-        <f t="shared" si="190"/>
+        <f t="shared" si="191"/>
         <v>62.128086312000008</v>
       </c>
       <c r="AG108" s="5">
-        <f t="shared" si="190"/>
+        <f t="shared" si="191"/>
         <v>63.991928901360012</v>
       </c>
       <c r="AH108" s="5">
-        <f t="shared" si="190"/>
+        <f t="shared" si="191"/>
         <v>65.911686768400813</v>
       </c>
       <c r="AI108" s="5">
-        <f t="shared" si="190"/>
+        <f t="shared" si="191"/>
         <v>67.889037371452844</v>
       </c>
       <c r="AJ108" s="5">
-        <f t="shared" si="190"/>
+        <f t="shared" si="191"/>
         <v>69.925708492596428</v>
       </c>
       <c r="AK108" s="5">
-        <f t="shared" si="190"/>
+        <f t="shared" si="191"/>
         <v>72.023479747374324</v>
       </c>
       <c r="AL108" s="5">
-        <f t="shared" si="190"/>
+        <f t="shared" si="191"/>
         <v>74.184184139795562</v>
       </c>
     </row>
@@ -10068,7 +10070,7 @@
         <v>0</v>
       </c>
       <c r="N109" s="5">
-        <f t="shared" si="189"/>
+        <f t="shared" si="190"/>
         <v>1.6999999999999993</v>
       </c>
       <c r="O109" s="5">
@@ -10103,7 +10105,7 @@
         <v>15.7</v>
       </c>
       <c r="AB109" s="5">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>9.1</v>
       </c>
       <c r="AC109" s="5">
@@ -10145,37 +10147,37 @@
         <v>0.2</v>
       </c>
       <c r="H110" s="5">
-        <f t="shared" ref="H110:H130" si="191">H149-G110</f>
+        <f t="shared" ref="H110:H130" si="192">H149-G110</f>
         <v>0.7</v>
       </c>
       <c r="I110" s="5">
-        <f t="shared" ref="I110:I130" si="192">I149-H110-G110</f>
+        <f t="shared" ref="I110:I130" si="193">I149-H110-G110</f>
         <v>0</v>
       </c>
       <c r="J110" s="5">
-        <f t="shared" ref="J110:J130" si="193">J149-I110-H110-G110</f>
+        <f t="shared" ref="J110:J130" si="194">J149-I110-H110-G110</f>
         <v>7.5</v>
       </c>
       <c r="K110" s="5">
         <v>-1.4</v>
       </c>
       <c r="L110" s="5">
-        <f t="shared" ref="K110:M131" si="194">L149-K110</f>
+        <f t="shared" ref="K110:M131" si="195">L149-K110</f>
         <v>9.9999999999999867E-2</v>
       </c>
       <c r="M110" s="5">
-        <f t="shared" ref="M110:M130" si="195">M149-L110-K110</f>
+        <f t="shared" ref="M110:M130" si="196">M149-L110-K110</f>
         <v>-0.19999999999999996</v>
       </c>
       <c r="N110" s="5">
-        <f t="shared" si="189"/>
+        <f t="shared" si="190"/>
         <v>30.399999999999995</v>
       </c>
       <c r="O110" s="5">
         <v>0</v>
       </c>
       <c r="P110" s="5">
-        <f t="shared" ref="P110:P131" si="196">P149-O110</f>
+        <f t="shared" ref="P110:P131" si="197">P149-O110</f>
         <v>4.7</v>
       </c>
       <c r="Q110">
@@ -10203,7 +10205,7 @@
         <v>28.9</v>
       </c>
       <c r="AB110" s="5">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>4.7</v>
       </c>
       <c r="AC110" s="5">
@@ -10245,37 +10247,37 @@
         <v>0.6</v>
       </c>
       <c r="H111" s="5">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>0.6</v>
       </c>
       <c r="I111" s="5">
-        <f t="shared" si="192"/>
-        <v>0.50000000000000011</v>
-      </c>
-      <c r="J111" s="5">
         <f t="shared" si="193"/>
         <v>0.50000000000000011</v>
       </c>
+      <c r="J111" s="5">
+        <f t="shared" si="194"/>
+        <v>0.50000000000000011</v>
+      </c>
       <c r="K111" s="5">
         <v>0.3</v>
       </c>
       <c r="L111" s="5">
-        <f t="shared" si="194"/>
-        <v>-1</v>
-      </c>
-      <c r="M111" s="5">
         <f t="shared" si="195"/>
         <v>-1</v>
       </c>
+      <c r="M111" s="5">
+        <f t="shared" si="196"/>
+        <v>-1</v>
+      </c>
       <c r="N111" s="5">
-        <f t="shared" si="189"/>
+        <f t="shared" si="190"/>
         <v>-1.0999999999999999</v>
       </c>
       <c r="O111" s="5">
         <v>-0.3</v>
       </c>
       <c r="P111" s="5">
-        <f t="shared" si="196"/>
+        <f t="shared" si="197"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="Q111">
@@ -10303,7 +10305,7 @@
         <v>-2.8</v>
       </c>
       <c r="AB111" s="5">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>-0.2</v>
       </c>
       <c r="AC111" s="5">
@@ -10345,37 +10347,37 @@
         <v>14.2</v>
       </c>
       <c r="H112" s="5">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>0.10000000000000142</v>
       </c>
       <c r="I112" s="5">
-        <f t="shared" si="192"/>
+        <f t="shared" si="193"/>
         <v>-1.6000000000000014</v>
       </c>
       <c r="J112" s="5">
-        <f t="shared" si="193"/>
+        <f t="shared" si="194"/>
         <v>-1.5</v>
       </c>
       <c r="K112" s="5">
         <v>4.5</v>
       </c>
       <c r="L112" s="5">
-        <f t="shared" si="194"/>
+        <f t="shared" si="195"/>
         <v>5.8000000000000007</v>
       </c>
       <c r="M112" s="5">
-        <f t="shared" si="195"/>
+        <f t="shared" si="196"/>
         <v>6</v>
       </c>
       <c r="N112" s="5">
-        <f t="shared" si="189"/>
+        <f t="shared" si="190"/>
         <v>22.7</v>
       </c>
       <c r="O112" s="5">
         <v>9.1</v>
       </c>
       <c r="P112" s="5">
-        <f t="shared" si="196"/>
+        <f t="shared" si="197"/>
         <v>9.5000000000000018</v>
       </c>
       <c r="Q112">
@@ -10395,7 +10397,7 @@
         <v>39</v>
       </c>
       <c r="AB112" s="5">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>18.600000000000001</v>
       </c>
       <c r="AC112" s="5">
@@ -10437,37 +10439,37 @@
         <v>-0.9</v>
       </c>
       <c r="H113" s="5">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>2.4</v>
       </c>
       <c r="I113" s="5">
-        <f t="shared" si="192"/>
+        <f t="shared" si="193"/>
         <v>-2.1</v>
       </c>
       <c r="J113" s="5">
-        <f t="shared" si="193"/>
+        <f t="shared" si="194"/>
         <v>-7.9</v>
       </c>
       <c r="K113" s="5">
         <v>0.2</v>
       </c>
       <c r="L113" s="5">
-        <f t="shared" si="194"/>
+        <f t="shared" si="195"/>
         <v>-0.4</v>
       </c>
       <c r="M113" s="5">
-        <f t="shared" si="195"/>
+        <f t="shared" si="196"/>
         <v>0.10000000000000003</v>
       </c>
       <c r="N113" s="5">
-        <f t="shared" si="189"/>
+        <f t="shared" si="190"/>
         <v>-3.1000000000000005</v>
       </c>
       <c r="O113" s="5">
         <v>0</v>
       </c>
       <c r="P113" s="5">
-        <f t="shared" si="196"/>
+        <f t="shared" si="197"/>
         <v>0</v>
       </c>
       <c r="Q113">
@@ -10493,7 +10495,7 @@
         <v>-3.2</v>
       </c>
       <c r="AB113" s="5">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>0</v>
       </c>
       <c r="AC113" s="5">
@@ -10535,37 +10537,37 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="H114" s="5">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>10</v>
       </c>
       <c r="I114" s="5">
-        <f t="shared" si="192"/>
+        <f t="shared" si="193"/>
         <v>0.5999999999999992</v>
       </c>
       <c r="J114" s="5">
-        <f t="shared" si="193"/>
+        <f t="shared" si="194"/>
         <v>257.79999999999995</v>
       </c>
       <c r="K114" s="5">
         <v>0.3</v>
       </c>
       <c r="L114" s="5">
-        <f t="shared" si="194"/>
+        <f t="shared" si="195"/>
         <v>3.9000000000000004</v>
       </c>
       <c r="M114" s="5">
-        <f t="shared" si="195"/>
+        <f t="shared" si="196"/>
         <v>4.2</v>
       </c>
       <c r="N114" s="5">
-        <f t="shared" si="189"/>
+        <f t="shared" si="190"/>
         <v>940.9</v>
       </c>
       <c r="O114" s="5">
         <v>1.1000000000000001</v>
       </c>
       <c r="P114" s="5">
-        <f t="shared" si="196"/>
+        <f t="shared" si="197"/>
         <v>20.599999999999998</v>
       </c>
       <c r="Q114">
@@ -10592,7 +10594,7 @@
         <v>949.3</v>
       </c>
       <c r="AB114" s="5">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>21.7</v>
       </c>
       <c r="AC114" s="5">
@@ -10634,37 +10636,37 @@
         <v>0.2</v>
       </c>
       <c r="H115" s="5">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>0.7</v>
       </c>
       <c r="I115" s="5">
-        <f t="shared" si="192"/>
+        <f t="shared" si="193"/>
         <v>34.999999999999993</v>
       </c>
       <c r="J115" s="5">
-        <f t="shared" si="193"/>
+        <f t="shared" si="194"/>
         <v>20.70000000000001</v>
       </c>
       <c r="K115" s="5">
         <v>3.8</v>
       </c>
       <c r="L115" s="5">
-        <f t="shared" si="194"/>
+        <f t="shared" si="195"/>
         <v>3.5</v>
       </c>
       <c r="M115" s="5">
-        <f t="shared" si="195"/>
+        <f t="shared" si="196"/>
         <v>-7.8999999999999995</v>
       </c>
       <c r="N115" s="5">
-        <f t="shared" si="189"/>
+        <f t="shared" si="190"/>
         <v>-2.4000000000000004</v>
       </c>
       <c r="O115" s="5">
         <v>-2.9</v>
       </c>
       <c r="P115" s="5">
-        <f t="shared" si="196"/>
+        <f t="shared" si="197"/>
         <v>-22.900000000000002</v>
       </c>
       <c r="Q115">
@@ -10690,7 +10692,7 @@
         <v>-3</v>
       </c>
       <c r="AB115" s="5">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>-25.8</v>
       </c>
       <c r="AC115" s="5">
@@ -10730,33 +10732,33 @@
       </c>
       <c r="G116" s="5"/>
       <c r="H116" s="5">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>0</v>
       </c>
       <c r="I116" s="5">
-        <f t="shared" si="192"/>
+        <f t="shared" si="193"/>
         <v>0</v>
       </c>
       <c r="J116" s="5">
-        <f t="shared" si="193"/>
+        <f t="shared" si="194"/>
         <v>0</v>
       </c>
       <c r="K116" s="5"/>
       <c r="L116" s="5">
-        <f t="shared" si="194"/>
+        <f t="shared" si="195"/>
         <v>0</v>
       </c>
       <c r="M116" s="5">
-        <f t="shared" si="195"/>
+        <f t="shared" si="196"/>
         <v>2.5</v>
       </c>
       <c r="N116" s="5">
-        <f t="shared" si="189"/>
+        <f t="shared" si="190"/>
         <v>0.39999999999999991</v>
       </c>
       <c r="O116" s="5"/>
       <c r="P116" s="5">
-        <f t="shared" si="196"/>
+        <f t="shared" si="197"/>
         <v>0</v>
       </c>
       <c r="Q116">
@@ -10776,7 +10778,7 @@
         <v>2.9</v>
       </c>
       <c r="AB116" s="5">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>0</v>
       </c>
       <c r="AC116" s="5">
@@ -10818,37 +10820,37 @@
         <v>8.8000000000000007</v>
       </c>
       <c r="H117" s="5">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>15.3</v>
       </c>
       <c r="I117" s="5">
-        <f t="shared" si="192"/>
+        <f t="shared" si="193"/>
         <v>2.1999999999999993</v>
       </c>
       <c r="J117" s="5">
-        <f t="shared" si="193"/>
+        <f t="shared" si="194"/>
         <v>3.6999999999999993</v>
       </c>
       <c r="K117" s="5">
         <v>-9.1999999999999993</v>
       </c>
       <c r="L117" s="5">
-        <f t="shared" si="194"/>
+        <f t="shared" si="195"/>
         <v>3.7999999999999989</v>
       </c>
       <c r="M117" s="5">
-        <f t="shared" si="195"/>
+        <f t="shared" si="196"/>
         <v>0.10000000000000142</v>
       </c>
       <c r="N117" s="5">
-        <f t="shared" si="189"/>
+        <f t="shared" si="190"/>
         <v>-10.500000000000004</v>
       </c>
       <c r="O117" s="5">
         <v>11.8</v>
       </c>
       <c r="P117" s="5">
-        <f t="shared" si="196"/>
+        <f t="shared" si="197"/>
         <v>-23.8</v>
       </c>
       <c r="Q117">
@@ -10874,7 +10876,7 @@
         <v>-15.8</v>
       </c>
       <c r="AB117" s="5">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>-12</v>
       </c>
       <c r="AC117" s="5">
@@ -10916,35 +10918,35 @@
         <v>0</v>
       </c>
       <c r="H118" s="5">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>-0.3</v>
       </c>
       <c r="I118" s="5">
-        <f t="shared" si="192"/>
+        <f t="shared" si="193"/>
         <v>0</v>
       </c>
       <c r="J118" s="5">
-        <f t="shared" si="193"/>
+        <f t="shared" si="194"/>
         <v>13.100000000000001</v>
       </c>
       <c r="K118" s="5">
         <v>0</v>
       </c>
       <c r="L118" s="5">
-        <f t="shared" si="194"/>
+        <f t="shared" si="195"/>
         <v>0</v>
       </c>
       <c r="M118" s="5">
-        <f t="shared" si="195"/>
+        <f t="shared" si="196"/>
         <v>0</v>
       </c>
       <c r="N118" s="5">
-        <f t="shared" si="189"/>
+        <f t="shared" si="190"/>
         <v>0</v>
       </c>
       <c r="O118" s="5"/>
       <c r="P118" s="5">
-        <f t="shared" si="196"/>
+        <f t="shared" si="197"/>
         <v>48.2</v>
       </c>
       <c r="Q118">
@@ -10970,7 +10972,7 @@
         <v>0</v>
       </c>
       <c r="AB118" s="5">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>48.2</v>
       </c>
       <c r="AC118" s="5">
@@ -11010,33 +11012,33 @@
       </c>
       <c r="G119" s="5"/>
       <c r="H119" s="5">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>0</v>
       </c>
       <c r="I119" s="5">
-        <f t="shared" si="192"/>
+        <f t="shared" si="193"/>
         <v>10.8</v>
       </c>
       <c r="J119" s="5">
-        <f t="shared" si="193"/>
+        <f t="shared" si="194"/>
         <v>-10.8</v>
       </c>
       <c r="K119" s="5"/>
       <c r="L119" s="5">
-        <f t="shared" si="194"/>
+        <f t="shared" si="195"/>
         <v>0</v>
       </c>
       <c r="M119" s="5">
-        <f t="shared" si="195"/>
+        <f t="shared" si="196"/>
         <v>0</v>
       </c>
       <c r="N119" s="5">
-        <f t="shared" si="189"/>
+        <f t="shared" si="190"/>
         <v>0</v>
       </c>
       <c r="O119" s="5"/>
       <c r="P119" s="5">
-        <f t="shared" si="196"/>
+        <f t="shared" si="197"/>
         <v>0</v>
       </c>
       <c r="Q119">
@@ -11052,7 +11054,7 @@
       <c r="Z119" s="5"/>
       <c r="AA119" s="5"/>
       <c r="AB119" s="5">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>0</v>
       </c>
       <c r="AC119" s="5">
@@ -11094,35 +11096,35 @@
         <v>-5.9</v>
       </c>
       <c r="H120" s="5">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>0</v>
       </c>
       <c r="I120" s="5">
-        <f t="shared" si="192"/>
+        <f t="shared" si="193"/>
         <v>0.80000000000000071</v>
       </c>
       <c r="J120" s="5">
-        <f t="shared" si="193"/>
+        <f t="shared" si="194"/>
         <v>-1.5</v>
       </c>
       <c r="K120" s="5">
         <v>0</v>
       </c>
       <c r="L120" s="5">
-        <f t="shared" si="194"/>
+        <f t="shared" si="195"/>
         <v>0</v>
       </c>
       <c r="M120" s="5">
-        <f t="shared" si="195"/>
+        <f t="shared" si="196"/>
         <v>0</v>
       </c>
       <c r="N120" s="5">
-        <f t="shared" si="189"/>
+        <f t="shared" si="190"/>
         <v>0</v>
       </c>
       <c r="O120" s="5"/>
       <c r="P120" s="5">
-        <f t="shared" si="196"/>
+        <f t="shared" si="197"/>
         <v>0</v>
       </c>
       <c r="Q120">
@@ -11150,7 +11152,7 @@
         <v>0</v>
       </c>
       <c r="AB120" s="5">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>0</v>
       </c>
       <c r="AC120" s="5">
@@ -11192,37 +11194,37 @@
         <v>-2.7</v>
       </c>
       <c r="H121" s="5">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>-2.8999999999999995</v>
       </c>
       <c r="I121" s="5">
-        <f t="shared" si="192"/>
+        <f t="shared" si="193"/>
         <v>-2.1000000000000005</v>
       </c>
       <c r="J121" s="5">
-        <f t="shared" si="193"/>
+        <f t="shared" si="194"/>
         <v>-1.8999999999999995</v>
       </c>
       <c r="K121" s="5">
         <v>-1.3</v>
       </c>
       <c r="L121" s="5">
-        <f t="shared" si="194"/>
+        <f t="shared" si="195"/>
         <v>-1.2</v>
       </c>
       <c r="M121" s="5">
-        <f t="shared" si="195"/>
+        <f t="shared" si="196"/>
         <v>-0.99999999999999978</v>
       </c>
       <c r="N121" s="5">
-        <f t="shared" si="189"/>
+        <f t="shared" si="190"/>
         <v>0</v>
       </c>
       <c r="O121" s="5">
         <v>0</v>
       </c>
       <c r="P121" s="5">
-        <f t="shared" si="196"/>
+        <f t="shared" si="197"/>
         <v>0</v>
       </c>
       <c r="Q121">
@@ -11248,7 +11250,7 @@
         <v>-3.5</v>
       </c>
       <c r="AB121" s="5">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>0</v>
       </c>
       <c r="AC121" s="5">
@@ -11290,37 +11292,37 @@
         <v>-5.0999999999999996</v>
       </c>
       <c r="H122" s="5">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>-3.8000000000000007</v>
       </c>
       <c r="I122" s="5">
-        <f t="shared" si="192"/>
+        <f t="shared" si="193"/>
         <v>-9.9999999999999645E-2</v>
       </c>
       <c r="J122" s="5">
-        <f t="shared" si="193"/>
+        <f t="shared" si="194"/>
         <v>-2.4000000000000004</v>
       </c>
       <c r="K122" s="5">
         <v>0</v>
       </c>
       <c r="L122" s="5">
-        <f t="shared" si="194"/>
+        <f t="shared" si="195"/>
         <v>0</v>
       </c>
       <c r="M122" s="5">
-        <f t="shared" si="195"/>
+        <f t="shared" si="196"/>
         <v>0</v>
       </c>
       <c r="N122" s="5">
-        <f t="shared" si="189"/>
+        <f t="shared" si="190"/>
         <v>3.4</v>
       </c>
       <c r="O122" s="5">
         <v>7.3</v>
       </c>
       <c r="P122" s="5">
-        <f t="shared" si="196"/>
+        <f t="shared" si="197"/>
         <v>-9.1999999999999993</v>
       </c>
       <c r="Q122">
@@ -11349,7 +11351,7 @@
         <v>3.4</v>
       </c>
       <c r="AB122" s="5">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>-1.8999999999999995</v>
       </c>
       <c r="AC122" s="5">
@@ -11391,37 +11393,37 @@
         <v>5.3</v>
       </c>
       <c r="H123" s="5">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>7.6000000000000005</v>
       </c>
       <c r="I123" s="5">
-        <f t="shared" si="192"/>
+        <f t="shared" si="193"/>
         <v>7.0999999999999988</v>
       </c>
       <c r="J123" s="5">
-        <f t="shared" si="193"/>
+        <f t="shared" si="194"/>
         <v>21.799999999999994</v>
       </c>
       <c r="K123" s="5">
         <v>13.1</v>
       </c>
       <c r="L123" s="5">
-        <f t="shared" si="194"/>
+        <f t="shared" si="195"/>
         <v>7.2999999999999989</v>
       </c>
       <c r="M123" s="5">
-        <f t="shared" si="195"/>
+        <f t="shared" si="196"/>
         <v>8.6000000000000032</v>
       </c>
       <c r="N123" s="5">
-        <f t="shared" si="189"/>
+        <f t="shared" si="190"/>
         <v>3.2000000000000046</v>
       </c>
       <c r="O123" s="5">
         <v>2.4</v>
       </c>
       <c r="P123" s="5">
-        <f t="shared" si="196"/>
+        <f t="shared" si="197"/>
         <v>1</v>
       </c>
       <c r="Q123">
@@ -11449,7 +11451,7 @@
         <v>32.200000000000003</v>
       </c>
       <c r="AB123" s="5">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>3.4</v>
       </c>
       <c r="AC123" s="5">
@@ -11489,33 +11491,33 @@
       </c>
       <c r="G124" s="5"/>
       <c r="H124" s="5">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>0</v>
       </c>
       <c r="I124" s="5">
-        <f t="shared" si="192"/>
+        <f t="shared" si="193"/>
         <v>0</v>
       </c>
       <c r="J124" s="5">
-        <f t="shared" si="193"/>
+        <f t="shared" si="194"/>
         <v>0</v>
       </c>
       <c r="K124" s="5"/>
       <c r="L124" s="5">
-        <f t="shared" si="194"/>
+        <f t="shared" si="195"/>
         <v>0</v>
       </c>
       <c r="M124" s="5">
-        <f t="shared" si="195"/>
+        <f t="shared" si="196"/>
         <v>0.1</v>
       </c>
       <c r="N124" s="5">
-        <f t="shared" si="189"/>
+        <f t="shared" si="190"/>
         <v>1.5999999999999999</v>
       </c>
       <c r="O124" s="5"/>
       <c r="P124" s="5">
-        <f t="shared" si="196"/>
+        <f t="shared" si="197"/>
         <v>0</v>
       </c>
       <c r="Q124">
@@ -11535,7 +11537,7 @@
         <v>1.7</v>
       </c>
       <c r="AB124" s="5">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>0</v>
       </c>
       <c r="AC124" s="5">
@@ -11577,37 +11579,37 @@
         <v>1.5</v>
       </c>
       <c r="H125" s="5">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>-89.6</v>
       </c>
       <c r="I125" s="5">
-        <f t="shared" si="192"/>
+        <f t="shared" si="193"/>
         <v>53.399999999999991</v>
       </c>
       <c r="J125" s="5">
-        <f t="shared" si="193"/>
+        <f t="shared" si="194"/>
         <v>-88.1</v>
       </c>
       <c r="K125" s="5">
         <v>96.4</v>
       </c>
       <c r="L125" s="5">
-        <f t="shared" si="194"/>
+        <f t="shared" si="195"/>
         <v>-41.100000000000009</v>
       </c>
       <c r="M125" s="5">
-        <f t="shared" si="195"/>
+        <f t="shared" si="196"/>
         <v>22.700000000000003</v>
       </c>
       <c r="N125" s="5">
-        <f t="shared" si="189"/>
+        <f t="shared" si="190"/>
         <v>-20.299999999999997</v>
       </c>
       <c r="O125" s="5">
         <v>12.3</v>
       </c>
       <c r="P125" s="5">
-        <f t="shared" si="196"/>
+        <f t="shared" si="197"/>
         <v>1.5</v>
       </c>
       <c r="Q125">
@@ -11635,7 +11637,7 @@
         <v>57.7</v>
       </c>
       <c r="AB125" s="5">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>13.8</v>
       </c>
       <c r="AC125" s="5">
@@ -11677,37 +11679,37 @@
         <v>-131.6</v>
       </c>
       <c r="H126" s="5">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>-138.1</v>
       </c>
       <c r="I126" s="5">
-        <f t="shared" si="192"/>
+        <f t="shared" si="193"/>
         <v>-142.00000000000003</v>
       </c>
       <c r="J126" s="5">
-        <f t="shared" si="193"/>
+        <f t="shared" si="194"/>
         <v>3.0999999999999659</v>
       </c>
       <c r="K126" s="5">
         <v>-38.299999999999997</v>
       </c>
       <c r="L126" s="5">
-        <f t="shared" si="194"/>
+        <f t="shared" si="195"/>
         <v>26.4</v>
       </c>
       <c r="M126" s="5">
-        <f t="shared" si="195"/>
+        <f t="shared" si="196"/>
         <v>42.8</v>
       </c>
       <c r="N126" s="5">
-        <f t="shared" si="189"/>
+        <f t="shared" si="190"/>
         <v>98.4</v>
       </c>
       <c r="O126" s="5">
         <v>-18.399999999999999</v>
       </c>
       <c r="P126" s="5">
-        <f t="shared" si="196"/>
+        <f t="shared" si="197"/>
         <v>34.799999999999997</v>
       </c>
       <c r="Q126">
@@ -11735,7 +11737,7 @@
         <v>129.30000000000001</v>
       </c>
       <c r="AB126" s="5">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>16.399999999999999</v>
       </c>
       <c r="AC126" s="5">
@@ -11777,37 +11779,37 @@
         <v>-14.7</v>
       </c>
       <c r="H127" s="5">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>-9.1000000000000014</v>
       </c>
       <c r="I127" s="5">
-        <f t="shared" si="192"/>
+        <f t="shared" si="193"/>
         <v>-15.2</v>
       </c>
       <c r="J127" s="5">
-        <f t="shared" si="193"/>
+        <f t="shared" si="194"/>
         <v>-1.2999999999999972</v>
       </c>
       <c r="K127" s="5">
         <v>1.4</v>
       </c>
       <c r="L127" s="5">
-        <f t="shared" si="194"/>
+        <f t="shared" si="195"/>
         <v>-4.3</v>
       </c>
       <c r="M127" s="5">
-        <f t="shared" si="195"/>
+        <f t="shared" si="196"/>
         <v>-11.9</v>
       </c>
       <c r="N127" s="5">
-        <f t="shared" si="189"/>
+        <f t="shared" si="190"/>
         <v>12.299999999999999</v>
       </c>
       <c r="O127" s="5">
         <v>0.6</v>
       </c>
       <c r="P127" s="5">
-        <f t="shared" si="196"/>
+        <f t="shared" si="197"/>
         <v>-5.8</v>
       </c>
       <c r="Q127">
@@ -11833,7 +11835,7 @@
         <v>-2.5</v>
       </c>
       <c r="AB127" s="5">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>-5.2</v>
       </c>
       <c r="AC127" s="5">
@@ -11875,37 +11877,37 @@
         <v>-5.5</v>
       </c>
       <c r="H128" s="5">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>14.7</v>
       </c>
       <c r="I128" s="5">
-        <f t="shared" si="192"/>
+        <f t="shared" si="193"/>
         <v>-15.600000000000001</v>
       </c>
       <c r="J128" s="5">
-        <f t="shared" si="193"/>
+        <f t="shared" si="194"/>
         <v>38.900000000000006</v>
       </c>
       <c r="K128" s="5">
         <v>-14.5</v>
       </c>
       <c r="L128" s="5">
-        <f t="shared" si="194"/>
+        <f t="shared" si="195"/>
         <v>-6.3999999999999986</v>
       </c>
       <c r="M128" s="5">
-        <f t="shared" si="195"/>
+        <f t="shared" si="196"/>
         <v>-21.9</v>
       </c>
       <c r="N128" s="5">
-        <f t="shared" si="189"/>
+        <f t="shared" si="190"/>
         <v>11.599999999999998</v>
       </c>
       <c r="O128" s="5">
         <v>40.6</v>
       </c>
       <c r="P128" s="5">
-        <f t="shared" si="196"/>
+        <f t="shared" si="197"/>
         <v>1.1000000000000014</v>
       </c>
       <c r="Q128">
@@ -11933,7 +11935,7 @@
         <v>-31.2</v>
       </c>
       <c r="AB128" s="5">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>41.7</v>
       </c>
       <c r="AC128" s="5">
@@ -11967,7 +11969,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="2:38" x14ac:dyDescent="0.3">
+    <row r="129" spans="2:156" x14ac:dyDescent="0.3">
       <c r="B129" t="s">
         <v>90</v>
       </c>
@@ -11975,37 +11977,37 @@
         <v>13.8</v>
       </c>
       <c r="H129" s="5">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>-14.5</v>
       </c>
       <c r="I129" s="5">
-        <f t="shared" si="192"/>
+        <f t="shared" si="193"/>
         <v>21.900000000000002</v>
       </c>
       <c r="J129" s="5">
-        <f t="shared" si="193"/>
+        <f t="shared" si="194"/>
         <v>0.49999999999999645</v>
       </c>
       <c r="K129" s="5">
         <v>25.8</v>
       </c>
       <c r="L129" s="5">
-        <f t="shared" si="194"/>
+        <f t="shared" si="195"/>
         <v>-41.6</v>
       </c>
       <c r="M129" s="5">
-        <f t="shared" si="195"/>
+        <f t="shared" si="196"/>
         <v>-13.399999999999999</v>
       </c>
       <c r="N129" s="5">
-        <f t="shared" si="189"/>
+        <f t="shared" si="190"/>
         <v>-30.3</v>
       </c>
       <c r="O129" s="5">
         <v>-47.6</v>
       </c>
       <c r="P129" s="5">
-        <f t="shared" si="196"/>
+        <f t="shared" si="197"/>
         <v>43.5</v>
       </c>
       <c r="Q129">
@@ -12033,7 +12035,7 @@
         <v>-59.5</v>
       </c>
       <c r="AB129" s="5">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>-4.1000000000000014</v>
       </c>
       <c r="AC129" s="5">
@@ -12067,7 +12069,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="2:38" x14ac:dyDescent="0.3">
+    <row r="130" spans="2:156" x14ac:dyDescent="0.3">
       <c r="B130" t="s">
         <v>94</v>
       </c>
@@ -12075,37 +12077,37 @@
         <v>0</v>
       </c>
       <c r="H130" s="5">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>-2.9</v>
       </c>
       <c r="I130" s="5">
-        <f t="shared" si="192"/>
+        <f t="shared" si="193"/>
         <v>0</v>
       </c>
       <c r="J130" s="5">
-        <f t="shared" si="193"/>
+        <f t="shared" si="194"/>
         <v>0</v>
       </c>
       <c r="K130" s="5">
         <v>-9.1999999999999993</v>
       </c>
       <c r="L130" s="5">
-        <f t="shared" si="194"/>
+        <f t="shared" si="195"/>
         <v>0</v>
       </c>
       <c r="M130" s="5">
-        <f t="shared" si="195"/>
+        <f t="shared" si="196"/>
         <v>0</v>
       </c>
       <c r="N130" s="5">
-        <f t="shared" si="189"/>
+        <f t="shared" si="190"/>
         <v>-0.70000000000000107</v>
       </c>
       <c r="O130" s="5">
         <v>-6</v>
       </c>
       <c r="P130" s="5">
-        <f t="shared" si="196"/>
+        <f t="shared" si="197"/>
         <v>-2.3000000000000007</v>
       </c>
       <c r="Q130">
@@ -12125,7 +12127,7 @@
         <v>-9.9</v>
       </c>
       <c r="AB130" s="5">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>-8.3000000000000007</v>
       </c>
       <c r="AC130" s="5">
@@ -12159,7 +12161,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="2:38" x14ac:dyDescent="0.3">
+    <row r="131" spans="2:156" x14ac:dyDescent="0.3">
       <c r="B131" t="s">
         <v>114</v>
       </c>
@@ -12168,26 +12170,26 @@
       <c r="I131" s="5"/>
       <c r="J131" s="5"/>
       <c r="K131" s="5">
-        <f t="shared" si="194"/>
+        <f t="shared" si="195"/>
         <v>0</v>
       </c>
       <c r="L131" s="5">
-        <f t="shared" si="194"/>
+        <f t="shared" si="195"/>
         <v>0</v>
       </c>
       <c r="M131" s="5">
-        <f t="shared" si="194"/>
+        <f t="shared" si="195"/>
         <v>0</v>
       </c>
       <c r="N131" s="5">
-        <f t="shared" si="189"/>
+        <f t="shared" si="190"/>
         <v>-5.3</v>
       </c>
       <c r="O131" s="5">
         <v>-5.6</v>
       </c>
       <c r="P131" s="5">
-        <f t="shared" si="196"/>
+        <f t="shared" si="197"/>
         <v>-5.5</v>
       </c>
       <c r="Q131">
@@ -12207,7 +12209,7 @@
         <v>-5.3</v>
       </c>
       <c r="AB131" s="5">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>-11.1</v>
       </c>
       <c r="AC131" s="5">
@@ -12241,7 +12243,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="2:38" x14ac:dyDescent="0.3">
+    <row r="132" spans="2:156" x14ac:dyDescent="0.3">
       <c r="B132" t="s">
         <v>100</v>
       </c>
@@ -12272,7 +12274,7 @@
         <v>-53.900000000000006</v>
       </c>
       <c r="N132" s="5">
-        <f t="shared" si="189"/>
+        <f t="shared" si="190"/>
         <v>10.700000000000003</v>
       </c>
       <c r="O132" s="5">
@@ -12307,7 +12309,7 @@
         <v>-85.7</v>
       </c>
       <c r="AB132" s="5">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>-54.900000000000006</v>
       </c>
       <c r="AC132" s="5">
@@ -12341,128 +12343,128 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="2:38" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="2:156" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B133" s="1" t="s">
         <v>118</v>
       </c>
       <c r="G133" s="9">
-        <f t="shared" ref="G133:N133" si="197">G104+SUM(G105:G132)</f>
+        <f t="shared" ref="G133:N133" si="198">G104+SUM(G105:G132)</f>
         <v>-276.89999999999998</v>
       </c>
       <c r="H133" s="9">
-        <f t="shared" si="197"/>
+        <f t="shared" si="198"/>
         <v>-348</v>
       </c>
       <c r="I133" s="9">
-        <f t="shared" si="197"/>
+        <f t="shared" si="198"/>
         <v>-239.00000000000003</v>
       </c>
       <c r="J133" s="9">
-        <f t="shared" si="197"/>
+        <f t="shared" si="198"/>
         <v>-242.80000000000024</v>
       </c>
       <c r="K133" s="9">
-        <f t="shared" si="197"/>
+        <f t="shared" si="198"/>
         <v>-167.6</v>
       </c>
       <c r="L133" s="9">
-        <f t="shared" si="197"/>
+        <f t="shared" si="198"/>
         <v>-254.59999999999997</v>
       </c>
       <c r="M133" s="9">
-        <f t="shared" si="197"/>
+        <f t="shared" si="198"/>
         <v>-174.9</v>
       </c>
       <c r="N133" s="9">
-        <f t="shared" si="197"/>
+        <f t="shared" si="198"/>
         <v>-131.40000000000009</v>
       </c>
       <c r="O133" s="9">
-        <f t="shared" ref="O133:R133" si="198">O104+SUM(O105:O132)</f>
+        <f t="shared" ref="O133:R133" si="199">O104+SUM(O105:O132)</f>
         <v>-177.1</v>
       </c>
       <c r="P133" s="9">
-        <f t="shared" si="198"/>
+        <f t="shared" si="199"/>
         <v>-120.40000000000002</v>
       </c>
       <c r="Q133" s="9">
-        <f t="shared" si="198"/>
+        <f t="shared" si="199"/>
         <v>-322.7</v>
       </c>
       <c r="R133" s="9">
-        <f t="shared" si="198"/>
+        <f t="shared" si="199"/>
         <v>-214.2715</v>
       </c>
       <c r="V133" s="9">
-        <f t="shared" ref="V133:AA133" si="199">V104+SUM(V105:V132)</f>
+        <f t="shared" ref="V133:AA133" si="200">V104+SUM(V105:V132)</f>
         <v>-45.100000000000023</v>
       </c>
       <c r="W133" s="9">
-        <f t="shared" si="199"/>
+        <f t="shared" si="200"/>
         <v>-155.50000000000011</v>
       </c>
       <c r="X133" s="9">
-        <f t="shared" si="199"/>
+        <f t="shared" si="200"/>
         <v>-358.2000000000001</v>
       </c>
       <c r="Y133" s="9">
-        <f t="shared" si="199"/>
+        <f t="shared" si="200"/>
         <v>-828.40000000000009</v>
       </c>
       <c r="Z133" s="9">
-        <f t="shared" si="199"/>
+        <f t="shared" si="200"/>
         <v>-1106.7</v>
       </c>
       <c r="AA133" s="9">
-        <f t="shared" si="199"/>
+        <f t="shared" si="200"/>
         <v>-728.5</v>
       </c>
       <c r="AB133" s="9">
-        <f t="shared" ref="AB133:AL133" si="200">AB104+SUM(AB105:AB132)</f>
+        <f t="shared" ref="AB133:AL133" si="201">AB104+SUM(AB105:AB132)</f>
         <v>-834.47149999999988</v>
       </c>
       <c r="AC133" s="9">
-        <f t="shared" si="200"/>
+        <f t="shared" si="201"/>
         <v>-379.67688450000003</v>
       </c>
       <c r="AD133" s="9">
-        <f t="shared" si="200"/>
+        <f t="shared" si="201"/>
         <v>-216.42709523999977</v>
       </c>
       <c r="AE133" s="9">
-        <f t="shared" si="200"/>
+        <f t="shared" si="201"/>
         <v>-53.993420849399769</v>
       </c>
       <c r="AF133" s="9">
-        <f t="shared" si="200"/>
+        <f t="shared" si="201"/>
         <v>16.921884031626334</v>
       </c>
       <c r="AG133" s="9">
-        <f t="shared" si="200"/>
+        <f t="shared" si="201"/>
         <v>79.096102067545985</v>
       </c>
       <c r="AH133" s="9">
-        <f t="shared" si="200"/>
+        <f t="shared" si="201"/>
         <v>137.28657253283279</v>
       </c>
       <c r="AI133" s="9">
-        <f t="shared" si="200"/>
+        <f t="shared" si="201"/>
         <v>195.94899896027647</v>
       </c>
       <c r="AJ133" s="9">
-        <f t="shared" si="200"/>
+        <f t="shared" si="201"/>
         <v>255.54273713509627</v>
       </c>
       <c r="AK133" s="9">
-        <f t="shared" si="200"/>
+        <f t="shared" si="201"/>
         <v>319.40365795429273</v>
       </c>
       <c r="AL133" s="9">
-        <f t="shared" si="200"/>
+        <f t="shared" si="201"/>
         <v>389.61592051154332</v>
       </c>
     </row>
-    <row r="134" spans="2:38" x14ac:dyDescent="0.3">
+    <row r="134" spans="2:156" x14ac:dyDescent="0.3">
       <c r="B134" t="s">
         <v>84</v>
       </c>
@@ -12493,14 +12495,14 @@
         <v>59.199999999999989</v>
       </c>
       <c r="N134" s="5">
-        <f t="shared" si="189"/>
+        <f t="shared" si="190"/>
         <v>34.000000000000028</v>
       </c>
       <c r="O134" s="5">
         <v>40.5</v>
       </c>
       <c r="P134" s="5">
-        <f t="shared" ref="P134:P135" si="201">P173-O134</f>
+        <f t="shared" ref="P134:P135" si="202">P173-O134</f>
         <v>38.599999999999994</v>
       </c>
       <c r="Q134" s="5">
@@ -12532,47 +12534,47 @@
         <v>159.1</v>
       </c>
       <c r="AC134" s="5">
-        <f t="shared" ref="AC134:AL134" si="202">AB134*1.01</f>
+        <f t="shared" ref="AC134:AL134" si="203">AB134*1.01</f>
         <v>160.691</v>
       </c>
       <c r="AD134" s="5">
-        <f t="shared" si="202"/>
+        <f t="shared" si="203"/>
         <v>162.29791</v>
       </c>
       <c r="AE134" s="5">
-        <f t="shared" si="202"/>
+        <f t="shared" si="203"/>
         <v>163.92088910000001</v>
       </c>
       <c r="AF134" s="5">
-        <f t="shared" si="202"/>
+        <f t="shared" si="203"/>
         <v>165.56009799100002</v>
       </c>
       <c r="AG134" s="5">
-        <f t="shared" si="202"/>
+        <f t="shared" si="203"/>
         <v>167.21569897091001</v>
       </c>
       <c r="AH134" s="5">
-        <f t="shared" si="202"/>
+        <f t="shared" si="203"/>
         <v>168.88785596061911</v>
       </c>
       <c r="AI134" s="5">
-        <f t="shared" si="202"/>
+        <f t="shared" si="203"/>
         <v>170.5767345202253</v>
       </c>
       <c r="AJ134" s="5">
-        <f t="shared" si="202"/>
+        <f t="shared" si="203"/>
         <v>172.28250186542755</v>
       </c>
       <c r="AK134" s="5">
-        <f t="shared" si="202"/>
+        <f t="shared" si="203"/>
         <v>174.00532688408182</v>
       </c>
       <c r="AL134" s="5">
-        <f t="shared" si="202"/>
+        <f t="shared" si="203"/>
         <v>175.74538015292265</v>
       </c>
     </row>
-    <row r="135" spans="2:38" x14ac:dyDescent="0.3">
+    <row r="135" spans="2:156" x14ac:dyDescent="0.3">
       <c r="B135" t="s">
         <v>119</v>
       </c>
@@ -12603,14 +12605,14 @@
         <v>30.5</v>
       </c>
       <c r="N135" s="5">
-        <f t="shared" si="189"/>
+        <f t="shared" si="190"/>
         <v>5.7000000000000028</v>
       </c>
       <c r="O135" s="5">
         <v>5.6</v>
       </c>
       <c r="P135" s="5">
-        <f t="shared" si="201"/>
+        <f t="shared" si="202"/>
         <v>1.8000000000000007</v>
       </c>
       <c r="Q135" s="5">
@@ -12642,47 +12644,47 @@
         <v>14.4</v>
       </c>
       <c r="AC135" s="5">
-        <f t="shared" ref="AC135:AL135" si="203">AB135*1.03</f>
+        <f t="shared" ref="AC135:AL135" si="204">AB135*1.03</f>
         <v>14.832000000000001</v>
       </c>
       <c r="AD135" s="5">
-        <f t="shared" si="203"/>
+        <f t="shared" si="204"/>
         <v>15.276960000000001</v>
       </c>
       <c r="AE135" s="5">
-        <f t="shared" si="203"/>
+        <f t="shared" si="204"/>
         <v>15.735268800000002</v>
       </c>
       <c r="AF135" s="5">
-        <f t="shared" si="203"/>
+        <f t="shared" si="204"/>
         <v>16.207326864000002</v>
       </c>
       <c r="AG135" s="5">
-        <f t="shared" si="203"/>
+        <f t="shared" si="204"/>
         <v>16.693546669920003</v>
       </c>
       <c r="AH135" s="5">
-        <f t="shared" si="203"/>
+        <f t="shared" si="204"/>
         <v>17.194353070017605</v>
       </c>
       <c r="AI135" s="5">
-        <f t="shared" si="203"/>
+        <f t="shared" si="204"/>
         <v>17.710183662118133</v>
       </c>
       <c r="AJ135" s="5">
-        <f t="shared" si="203"/>
+        <f t="shared" si="204"/>
         <v>18.241489171981677</v>
       </c>
       <c r="AK135" s="5">
-        <f t="shared" si="203"/>
+        <f t="shared" si="204"/>
         <v>18.788733847141128</v>
       </c>
       <c r="AL135" s="5">
-        <f t="shared" si="203"/>
+        <f t="shared" si="204"/>
         <v>19.352395862555362</v>
       </c>
     </row>
-    <row r="136" spans="2:38" x14ac:dyDescent="0.3">
+    <row r="136" spans="2:156" x14ac:dyDescent="0.3">
       <c r="B136" t="s">
         <v>129</v>
       </c>
@@ -12691,119 +12693,119 @@
         <v>180</v>
       </c>
       <c r="H136" s="5">
-        <f t="shared" ref="H136:N136" si="204">H134+H135</f>
+        <f t="shared" ref="H136:N136" si="205">H134+H135</f>
         <v>158.60000000000002</v>
       </c>
       <c r="I136" s="5">
-        <f t="shared" si="204"/>
+        <f t="shared" si="205"/>
         <v>171.49999999999997</v>
       </c>
       <c r="J136" s="5">
-        <f t="shared" si="204"/>
+        <f t="shared" si="205"/>
         <v>186.00000000000006</v>
       </c>
       <c r="K136" s="5">
-        <f t="shared" si="204"/>
+        <f t="shared" si="205"/>
         <v>98.699999999999989</v>
       </c>
       <c r="L136" s="5">
-        <f t="shared" si="204"/>
+        <f t="shared" si="205"/>
         <v>106.20000000000002</v>
       </c>
       <c r="M136" s="5">
-        <f t="shared" si="204"/>
+        <f t="shared" si="205"/>
         <v>89.699999999999989</v>
       </c>
       <c r="N136" s="5">
-        <f t="shared" si="204"/>
+        <f t="shared" si="205"/>
         <v>39.700000000000031</v>
       </c>
       <c r="O136" s="5">
-        <f t="shared" ref="O136:P136" si="205">O134+O135</f>
+        <f t="shared" ref="O136:P136" si="206">O134+O135</f>
         <v>46.1</v>
       </c>
       <c r="P136" s="5">
-        <f t="shared" si="205"/>
+        <f t="shared" si="206"/>
         <v>40.399999999999991</v>
       </c>
       <c r="Q136" s="5">
-        <f t="shared" ref="Q136:R136" si="206">Q134+Q135</f>
+        <f t="shared" ref="Q136:R136" si="207">Q134+Q135</f>
         <v>43</v>
       </c>
       <c r="R136" s="5">
-        <f t="shared" si="206"/>
+        <f t="shared" si="207"/>
         <v>44</v>
       </c>
       <c r="V136" s="5">
-        <f t="shared" ref="V136:W136" si="207">V134+V135</f>
+        <f t="shared" ref="V136:W136" si="208">V134+V135</f>
         <v>8.1</v>
       </c>
       <c r="W136" s="5">
-        <f t="shared" si="207"/>
+        <f t="shared" si="208"/>
         <v>48.2</v>
       </c>
       <c r="X136" s="5">
-        <f t="shared" ref="X136:Y136" si="208">X134+X135</f>
+        <f t="shared" ref="X136:Y136" si="209">X134+X135</f>
         <v>192.39999999999998</v>
       </c>
       <c r="Y136" s="5">
-        <f t="shared" si="208"/>
+        <f t="shared" si="209"/>
         <v>463.90000000000003</v>
       </c>
       <c r="Z136" s="5">
-        <f t="shared" ref="Z136:AA136" si="209">Z134+Z135</f>
+        <f t="shared" ref="Z136:AA136" si="210">Z134+Z135</f>
         <v>696.1</v>
       </c>
       <c r="AA136" s="5">
-        <f t="shared" si="209"/>
+        <f t="shared" si="210"/>
         <v>334.3</v>
       </c>
       <c r="AB136" s="5">
-        <f t="shared" ref="AB136:AL136" si="210">AB134+AB135</f>
+        <f t="shared" ref="AB136:AL136" si="211">AB134+AB135</f>
         <v>173.5</v>
       </c>
       <c r="AC136" s="5">
-        <f t="shared" si="210"/>
+        <f t="shared" si="211"/>
         <v>175.523</v>
       </c>
       <c r="AD136" s="5">
-        <f t="shared" si="210"/>
+        <f t="shared" si="211"/>
         <v>177.57487</v>
       </c>
       <c r="AE136" s="5">
-        <f t="shared" si="210"/>
+        <f t="shared" si="211"/>
         <v>179.65615790000001</v>
       </c>
       <c r="AF136" s="5">
-        <f t="shared" si="210"/>
+        <f t="shared" si="211"/>
         <v>181.76742485500003</v>
       </c>
       <c r="AG136" s="5">
-        <f t="shared" si="210"/>
+        <f t="shared" si="211"/>
         <v>183.90924564083002</v>
       </c>
       <c r="AH136" s="5">
-        <f t="shared" si="210"/>
+        <f t="shared" si="211"/>
         <v>186.0822090306367</v>
       </c>
       <c r="AI136" s="5">
-        <f t="shared" si="210"/>
+        <f t="shared" si="211"/>
         <v>188.28691818234344</v>
       </c>
       <c r="AJ136" s="5">
-        <f t="shared" si="210"/>
+        <f t="shared" si="211"/>
         <v>190.52399103740922</v>
       </c>
       <c r="AK136" s="5">
-        <f t="shared" si="210"/>
+        <f t="shared" si="211"/>
         <v>192.79406073122294</v>
       </c>
       <c r="AL136" s="5">
-        <f t="shared" si="210"/>
+        <f t="shared" si="211"/>
         <v>195.09777601547802</v>
       </c>
     </row>
-    <row r="137" spans="2:38" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="2:156" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B137" s="1" t="s">
         <v>120</v>
       </c>
@@ -12812,119 +12814,591 @@
         <v>-456.9</v>
       </c>
       <c r="H137" s="9">
-        <f t="shared" ref="H137:N137" si="211">H133-H136</f>
+        <f t="shared" ref="H137:N137" si="212">H133-H136</f>
         <v>-506.6</v>
       </c>
       <c r="I137" s="9">
-        <f t="shared" si="211"/>
+        <f t="shared" si="212"/>
         <v>-410.5</v>
       </c>
       <c r="J137" s="9">
-        <f t="shared" si="211"/>
+        <f t="shared" si="212"/>
         <v>-428.8000000000003</v>
       </c>
       <c r="K137" s="9">
-        <f t="shared" si="211"/>
+        <f t="shared" si="212"/>
         <v>-266.29999999999995</v>
       </c>
       <c r="L137" s="9">
-        <f t="shared" si="211"/>
+        <f t="shared" si="212"/>
         <v>-360.79999999999995</v>
       </c>
       <c r="M137" s="9">
-        <f t="shared" si="211"/>
+        <f t="shared" si="212"/>
         <v>-264.60000000000002</v>
       </c>
       <c r="N137" s="9">
-        <f t="shared" si="211"/>
+        <f t="shared" si="212"/>
         <v>-171.10000000000014</v>
       </c>
       <c r="O137" s="9">
-        <f t="shared" ref="O137:P137" si="212">O133-O136</f>
+        <f t="shared" ref="O137:P137" si="213">O133-O136</f>
         <v>-223.2</v>
       </c>
       <c r="P137" s="9">
-        <f t="shared" si="212"/>
+        <f t="shared" si="213"/>
         <v>-160.80000000000001</v>
       </c>
       <c r="Q137" s="9">
-        <f t="shared" ref="Q137:R137" si="213">Q133-Q136</f>
+        <f t="shared" ref="Q137:R137" si="214">Q133-Q136</f>
         <v>-365.7</v>
       </c>
       <c r="R137" s="9">
-        <f t="shared" si="213"/>
+        <f t="shared" si="214"/>
         <v>-258.2715</v>
       </c>
       <c r="V137" s="9">
-        <f t="shared" ref="V137:W137" si="214">V133-V136</f>
+        <f t="shared" ref="V137:W137" si="215">V133-V136</f>
         <v>-53.200000000000024</v>
       </c>
       <c r="W137" s="9">
-        <f t="shared" si="214"/>
+        <f t="shared" si="215"/>
         <v>-203.7000000000001</v>
       </c>
       <c r="X137" s="9">
-        <f t="shared" ref="X137:Y137" si="215">X133-X136</f>
+        <f t="shared" ref="X137:Y137" si="216">X133-X136</f>
         <v>-550.60000000000014</v>
       </c>
       <c r="Y137" s="9">
-        <f t="shared" si="215"/>
+        <f t="shared" si="216"/>
         <v>-1292.3000000000002</v>
       </c>
       <c r="Z137" s="9">
-        <f t="shared" ref="Z137:AA137" si="216">Z133-Z136</f>
+        <f t="shared" ref="Z137:AA137" si="217">Z133-Z136</f>
         <v>-1802.8000000000002</v>
       </c>
       <c r="AA137" s="9">
-        <f t="shared" si="216"/>
+        <f t="shared" si="217"/>
         <v>-1062.8</v>
       </c>
       <c r="AB137" s="9">
-        <f t="shared" ref="AB137:AL137" si="217">AB133-AB136</f>
+        <f t="shared" ref="AB137:AL137" si="218">AB133-AB136</f>
         <v>-1007.9714999999999</v>
       </c>
       <c r="AC137" s="9">
-        <f t="shared" si="217"/>
+        <f t="shared" si="218"/>
         <v>-555.19988450000005</v>
       </c>
       <c r="AD137" s="9">
-        <f t="shared" si="217"/>
+        <f t="shared" si="218"/>
         <v>-394.00196523999978</v>
       </c>
       <c r="AE137" s="9">
-        <f t="shared" si="217"/>
+        <f t="shared" si="218"/>
         <v>-233.64957874939978</v>
       </c>
       <c r="AF137" s="9">
-        <f t="shared" si="217"/>
+        <f t="shared" si="218"/>
         <v>-164.84554082337371</v>
       </c>
       <c r="AG137" s="9">
-        <f t="shared" si="217"/>
+        <f t="shared" si="218"/>
         <v>-104.81314357328404</v>
       </c>
       <c r="AH137" s="9">
-        <f t="shared" si="217"/>
+        <f t="shared" si="218"/>
         <v>-48.795636497803912</v>
       </c>
       <c r="AI137" s="9">
-        <f t="shared" si="217"/>
+        <f t="shared" si="218"/>
         <v>7.6620807779330278</v>
       </c>
       <c r="AJ137" s="9">
-        <f t="shared" si="217"/>
+        <f t="shared" si="218"/>
         <v>65.018746097687057</v>
       </c>
       <c r="AK137" s="9">
-        <f t="shared" si="217"/>
+        <f t="shared" si="218"/>
         <v>126.60959722306978</v>
       </c>
       <c r="AL137" s="9">
-        <f t="shared" si="217"/>
+        <f t="shared" si="218"/>
         <v>194.5181444960653</v>
       </c>
-    </row>
-    <row r="138" spans="2:38" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="AM137" s="1">
+        <f>AL137*(1+$AP$38)</f>
+        <v>192.57296305110464</v>
+      </c>
+      <c r="AN137" s="1">
+        <f t="shared" ref="AN137:CY137" si="219">AM137*(1+$AP$38)</f>
+        <v>190.64723342059358</v>
+      </c>
+      <c r="AO137" s="1">
+        <f t="shared" si="219"/>
+        <v>188.74076108638764</v>
+      </c>
+      <c r="AP137" s="1">
+        <f t="shared" si="219"/>
+        <v>186.85335347552376</v>
+      </c>
+      <c r="AQ137" s="1">
+        <f t="shared" si="219"/>
+        <v>184.98481994076852</v>
+      </c>
+      <c r="AR137" s="1">
+        <f t="shared" si="219"/>
+        <v>183.13497174136083</v>
+      </c>
+      <c r="AS137" s="1">
+        <f t="shared" si="219"/>
+        <v>181.30362202394721</v>
+      </c>
+      <c r="AT137" s="1">
+        <f t="shared" si="219"/>
+        <v>179.49058580370775</v>
+      </c>
+      <c r="AU137" s="1">
+        <f t="shared" si="219"/>
+        <v>177.69567994567066</v>
+      </c>
+      <c r="AV137" s="1">
+        <f t="shared" si="219"/>
+        <v>175.91872314621395</v>
+      </c>
+      <c r="AW137" s="1">
+        <f t="shared" si="219"/>
+        <v>174.15953591475181</v>
+      </c>
+      <c r="AX137" s="1">
+        <f t="shared" si="219"/>
+        <v>172.4179405556043</v>
+      </c>
+      <c r="AY137" s="1">
+        <f t="shared" si="219"/>
+        <v>170.69376115004826</v>
+      </c>
+      <c r="AZ137" s="1">
+        <f t="shared" si="219"/>
+        <v>168.98682353854778</v>
+      </c>
+      <c r="BA137" s="1">
+        <f t="shared" si="219"/>
+        <v>167.29695530316229</v>
+      </c>
+      <c r="BB137" s="1">
+        <f t="shared" si="219"/>
+        <v>165.62398575013066</v>
+      </c>
+      <c r="BC137" s="1">
+        <f t="shared" si="219"/>
+        <v>163.96774589262935</v>
+      </c>
+      <c r="BD137" s="1">
+        <f t="shared" si="219"/>
+        <v>162.32806843370307</v>
+      </c>
+      <c r="BE137" s="1">
+        <f t="shared" si="219"/>
+        <v>160.70478774936603</v>
+      </c>
+      <c r="BF137" s="1">
+        <f t="shared" si="219"/>
+        <v>159.09773987187236</v>
+      </c>
+      <c r="BG137" s="1">
+        <f t="shared" si="219"/>
+        <v>157.50676247315363</v>
+      </c>
+      <c r="BH137" s="1">
+        <f t="shared" si="219"/>
+        <v>155.9316948484221</v>
+      </c>
+      <c r="BI137" s="1">
+        <f t="shared" si="219"/>
+        <v>154.37237789993787</v>
+      </c>
+      <c r="BJ137" s="1">
+        <f t="shared" si="219"/>
+        <v>152.82865412093849</v>
+      </c>
+      <c r="BK137" s="1">
+        <f t="shared" si="219"/>
+        <v>151.30036757972911</v>
+      </c>
+      <c r="BL137" s="1">
+        <f t="shared" si="219"/>
+        <v>149.78736390393183</v>
+      </c>
+      <c r="BM137" s="1">
+        <f t="shared" si="219"/>
+        <v>148.28949026489252</v>
+      </c>
+      <c r="BN137" s="1">
+        <f t="shared" si="219"/>
+        <v>146.8065953622436</v>
+      </c>
+      <c r="BO137" s="1">
+        <f t="shared" si="219"/>
+        <v>145.33852940862116</v>
+      </c>
+      <c r="BP137" s="1">
+        <f t="shared" si="219"/>
+        <v>143.88514411453494</v>
+      </c>
+      <c r="BQ137" s="1">
+        <f t="shared" si="219"/>
+        <v>142.44629267338959</v>
+      </c>
+      <c r="BR137" s="1">
+        <f t="shared" si="219"/>
+        <v>141.0218297466557</v>
+      </c>
+      <c r="BS137" s="1">
+        <f t="shared" si="219"/>
+        <v>139.61161144918913</v>
+      </c>
+      <c r="BT137" s="1">
+        <f t="shared" si="219"/>
+        <v>138.21549533469724</v>
+      </c>
+      <c r="BU137" s="1">
+        <f t="shared" si="219"/>
+        <v>136.83334038135027</v>
+      </c>
+      <c r="BV137" s="1">
+        <f t="shared" si="219"/>
+        <v>135.46500697753677</v>
+      </c>
+      <c r="BW137" s="1">
+        <f t="shared" si="219"/>
+        <v>134.1103569077614</v>
+      </c>
+      <c r="BX137" s="1">
+        <f t="shared" si="219"/>
+        <v>132.7692533386838</v>
+      </c>
+      <c r="BY137" s="1">
+        <f t="shared" si="219"/>
+        <v>131.44156080529694</v>
+      </c>
+      <c r="BZ137" s="1">
+        <f t="shared" si="219"/>
+        <v>130.12714519724398</v>
+      </c>
+      <c r="CA137" s="1">
+        <f t="shared" si="219"/>
+        <v>128.82587374527154</v>
+      </c>
+      <c r="CB137" s="1">
+        <f t="shared" si="219"/>
+        <v>127.53761500781881</v>
+      </c>
+      <c r="CC137" s="1">
+        <f t="shared" si="219"/>
+        <v>126.26223885774063</v>
+      </c>
+      <c r="CD137" s="1">
+        <f t="shared" si="219"/>
+        <v>124.99961646916321</v>
+      </c>
+      <c r="CE137" s="1">
+        <f t="shared" si="219"/>
+        <v>123.74962030447158</v>
+      </c>
+      <c r="CF137" s="1">
+        <f t="shared" si="219"/>
+        <v>122.51212410142686</v>
+      </c>
+      <c r="CG137" s="1">
+        <f t="shared" si="219"/>
+        <v>121.2870028604126</v>
+      </c>
+      <c r="CH137" s="1">
+        <f t="shared" si="219"/>
+        <v>120.07413283180847</v>
+      </c>
+      <c r="CI137" s="1">
+        <f t="shared" si="219"/>
+        <v>118.87339150349038</v>
+      </c>
+      <c r="CJ137" s="1">
+        <f t="shared" si="219"/>
+        <v>117.68465758845548</v>
+      </c>
+      <c r="CK137" s="1">
+        <f t="shared" si="219"/>
+        <v>116.50781101257093</v>
+      </c>
+      <c r="CL137" s="1">
+        <f t="shared" si="219"/>
+        <v>115.34273290244522</v>
+      </c>
+      <c r="CM137" s="1">
+        <f t="shared" si="219"/>
+        <v>114.18930557342077</v>
+      </c>
+      <c r="CN137" s="1">
+        <f t="shared" si="219"/>
+        <v>113.04741251768655</v>
+      </c>
+      <c r="CO137" s="1">
+        <f t="shared" si="219"/>
+        <v>111.91693839250969</v>
+      </c>
+      <c r="CP137" s="1">
+        <f t="shared" si="219"/>
+        <v>110.79776900858459</v>
+      </c>
+      <c r="CQ137" s="1">
+        <f t="shared" si="219"/>
+        <v>109.68979131849875</v>
+      </c>
+      <c r="CR137" s="1">
+        <f t="shared" si="219"/>
+        <v>108.59289340531376</v>
+      </c>
+      <c r="CS137" s="1">
+        <f t="shared" si="219"/>
+        <v>107.50696447126062</v>
+      </c>
+      <c r="CT137" s="1">
+        <f t="shared" si="219"/>
+        <v>106.431894826548</v>
+      </c>
+      <c r="CU137" s="1">
+        <f t="shared" si="219"/>
+        <v>105.36757587828252</v>
+      </c>
+      <c r="CV137" s="1">
+        <f t="shared" si="219"/>
+        <v>104.31390011949969</v>
+      </c>
+      <c r="CW137" s="1">
+        <f t="shared" si="219"/>
+        <v>103.27076111830469</v>
+      </c>
+      <c r="CX137" s="1">
+        <f t="shared" si="219"/>
+        <v>102.23805350712165</v>
+      </c>
+      <c r="CY137" s="1">
+        <f t="shared" si="219"/>
+        <v>101.21567297205043</v>
+      </c>
+      <c r="CZ137" s="1">
+        <f t="shared" ref="CZ137:EZ137" si="220">CY137*(1+$AP$38)</f>
+        <v>100.20351624232993</v>
+      </c>
+      <c r="DA137" s="1">
+        <f t="shared" si="220"/>
+        <v>99.201481079906628</v>
+      </c>
+      <c r="DB137" s="1">
+        <f t="shared" si="220"/>
+        <v>98.209466269107565</v>
+      </c>
+      <c r="DC137" s="1">
+        <f t="shared" si="220"/>
+        <v>97.227371606416483</v>
+      </c>
+      <c r="DD137" s="1">
+        <f t="shared" si="220"/>
+        <v>96.255097890352317</v>
+      </c>
+      <c r="DE137" s="1">
+        <f t="shared" si="220"/>
+        <v>95.292546911448795</v>
+      </c>
+      <c r="DF137" s="1">
+        <f t="shared" si="220"/>
+        <v>94.339621442334305</v>
+      </c>
+      <c r="DG137" s="1">
+        <f t="shared" si="220"/>
+        <v>93.396225227910961</v>
+      </c>
+      <c r="DH137" s="1">
+        <f t="shared" si="220"/>
+        <v>92.462262975631845</v>
+      </c>
+      <c r="DI137" s="1">
+        <f t="shared" si="220"/>
+        <v>91.537640345875531</v>
+      </c>
+      <c r="DJ137" s="1">
+        <f t="shared" si="220"/>
+        <v>90.62226394241678</v>
+      </c>
+      <c r="DK137" s="1">
+        <f t="shared" si="220"/>
+        <v>89.716041302992608</v>
+      </c>
+      <c r="DL137" s="1">
+        <f t="shared" si="220"/>
+        <v>88.818880889962685</v>
+      </c>
+      <c r="DM137" s="1">
+        <f t="shared" si="220"/>
+        <v>87.930692081063057</v>
+      </c>
+      <c r="DN137" s="1">
+        <f t="shared" si="220"/>
+        <v>87.051385160252423</v>
+      </c>
+      <c r="DO137" s="1">
+        <f t="shared" si="220"/>
+        <v>86.180871308649898</v>
+      </c>
+      <c r="DP137" s="1">
+        <f t="shared" si="220"/>
+        <v>85.319062595563395</v>
+      </c>
+      <c r="DQ137" s="1">
+        <f t="shared" si="220"/>
+        <v>84.465871969607761</v>
+      </c>
+      <c r="DR137" s="1">
+        <f t="shared" si="220"/>
+        <v>83.621213249911676</v>
+      </c>
+      <c r="DS137" s="1">
+        <f t="shared" si="220"/>
+        <v>82.785001117412563</v>
+      </c>
+      <c r="DT137" s="1">
+        <f t="shared" si="220"/>
+        <v>81.957151106238442</v>
+      </c>
+      <c r="DU137" s="1">
+        <f t="shared" si="220"/>
+        <v>81.137579595176049</v>
+      </c>
+      <c r="DV137" s="1">
+        <f t="shared" si="220"/>
+        <v>80.326203799224288</v>
+      </c>
+      <c r="DW137" s="1">
+        <f t="shared" si="220"/>
+        <v>79.522941761232047</v>
+      </c>
+      <c r="DX137" s="1">
+        <f t="shared" si="220"/>
+        <v>78.727712343619729</v>
+      </c>
+      <c r="DY137" s="1">
+        <f t="shared" si="220"/>
+        <v>77.940435220183531</v>
+      </c>
+      <c r="DZ137" s="1">
+        <f t="shared" si="220"/>
+        <v>77.161030867981694</v>
+      </c>
+      <c r="EA137" s="1">
+        <f t="shared" si="220"/>
+        <v>76.389420559301882</v>
+      </c>
+      <c r="EB137" s="1">
+        <f t="shared" si="220"/>
+        <v>75.625526353708864</v>
+      </c>
+      <c r="EC137" s="1">
+        <f t="shared" si="220"/>
+        <v>74.869271090171779</v>
+      </c>
+      <c r="ED137" s="1">
+        <f t="shared" si="220"/>
+        <v>74.120578379270057</v>
+      </c>
+      <c r="EE137" s="1">
+        <f t="shared" si="220"/>
+        <v>73.379372595477349</v>
+      </c>
+      <c r="EF137" s="1">
+        <f t="shared" si="220"/>
+        <v>72.645578869522581</v>
+      </c>
+      <c r="EG137" s="1">
+        <f t="shared" si="220"/>
+        <v>71.919123080827347</v>
+      </c>
+      <c r="EH137" s="1">
+        <f t="shared" si="220"/>
+        <v>71.19993185001907</v>
+      </c>
+      <c r="EI137" s="1">
+        <f t="shared" si="220"/>
+        <v>70.487932531518879</v>
+      </c>
+      <c r="EJ137" s="1">
+        <f t="shared" si="220"/>
+        <v>69.783053206203689</v>
+      </c>
+      <c r="EK137" s="1">
+        <f t="shared" si="220"/>
+        <v>69.085222674141647</v>
+      </c>
+      <c r="EL137" s="1">
+        <f t="shared" si="220"/>
+        <v>68.394370447400235</v>
+      </c>
+      <c r="EM137" s="1">
+        <f t="shared" si="220"/>
+        <v>67.710426742926231</v>
+      </c>
+      <c r="EN137" s="1">
+        <f t="shared" si="220"/>
+        <v>67.033322475496973</v>
+      </c>
+      <c r="EO137" s="1">
+        <f t="shared" si="220"/>
+        <v>66.362989250742004</v>
+      </c>
+      <c r="EP137" s="1">
+        <f t="shared" si="220"/>
+        <v>65.699359358234588</v>
+      </c>
+      <c r="EQ137" s="1">
+        <f t="shared" si="220"/>
+        <v>65.042365764652246</v>
+      </c>
+      <c r="ER137" s="1">
+        <f t="shared" si="220"/>
+        <v>64.391942107005718</v>
+      </c>
+      <c r="ES137" s="1">
+        <f t="shared" si="220"/>
+        <v>63.748022685935659</v>
+      </c>
+      <c r="ET137" s="1">
+        <f t="shared" si="220"/>
+        <v>63.110542459076299</v>
+      </c>
+      <c r="EU137" s="1">
+        <f t="shared" si="220"/>
+        <v>62.479437034485535</v>
+      </c>
+      <c r="EV137" s="1">
+        <f t="shared" si="220"/>
+        <v>61.854642664140677</v>
+      </c>
+      <c r="EW137" s="1">
+        <f t="shared" si="220"/>
+        <v>61.236096237499268</v>
+      </c>
+      <c r="EX137" s="1">
+        <f t="shared" si="220"/>
+        <v>60.623735275124275</v>
+      </c>
+      <c r="EY137" s="1">
+        <f t="shared" si="220"/>
+        <v>60.017497922373032</v>
+      </c>
+      <c r="EZ137" s="1">
+        <f t="shared" si="220"/>
+        <v>59.417322943149301</v>
+      </c>
+    </row>
+    <row r="138" spans="2:156" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="G138" s="9"/>
       <c r="H138" s="9"/>
       <c r="I138" s="9"/>
@@ -12939,7 +13413,7 @@
       <c r="R138" s="9"/>
       <c r="Z138" s="9"/>
     </row>
-    <row r="139" spans="2:38" x14ac:dyDescent="0.3">
+    <row r="139" spans="2:156" x14ac:dyDescent="0.3">
       <c r="B139" t="s">
         <v>123</v>
       </c>
@@ -12957,7 +13431,7 @@
       <c r="R139" s="5"/>
       <c r="Z139" s="1"/>
     </row>
-    <row r="140" spans="2:38" x14ac:dyDescent="0.3">
+    <row r="140" spans="2:156" x14ac:dyDescent="0.3">
       <c r="B140" t="s">
         <v>130</v>
       </c>
@@ -12970,26 +13444,33 @@
         <v>-0.45166666666666677</v>
       </c>
       <c r="L140" s="10">
-        <f t="shared" ref="L140:O140" si="218">L136/H136-1</f>
+        <f t="shared" ref="L140:O140" si="221">L136/H136-1</f>
         <v>-0.33039092055485497</v>
       </c>
       <c r="M140" s="10">
-        <f t="shared" si="218"/>
+        <f t="shared" si="221"/>
         <v>-0.4769679300291545</v>
       </c>
       <c r="N140" s="10">
-        <f t="shared" si="218"/>
+        <f t="shared" si="221"/>
         <v>-0.78655913978494607</v>
       </c>
       <c r="O140" s="10">
-        <f t="shared" si="218"/>
+        <f t="shared" si="221"/>
         <v>-0.5329280648429584</v>
       </c>
       <c r="P140" s="5"/>
       <c r="Q140" s="5"/>
       <c r="R140" s="5"/>
-    </row>
-    <row r="141" spans="2:38" x14ac:dyDescent="0.3">
+      <c r="AO140" t="s">
+        <v>73</v>
+      </c>
+      <c r="AP140" s="15">
+        <f>NPV(AP39,AC137:EZ137)</f>
+        <v>-244.67618202776887</v>
+      </c>
+    </row>
+    <row r="141" spans="2:156" x14ac:dyDescent="0.3">
       <c r="B141" t="s">
         <v>124</v>
       </c>
@@ -13006,7 +13487,7 @@
       <c r="Q141" s="10"/>
       <c r="R141" s="10"/>
     </row>
-    <row r="143" spans="2:38" x14ac:dyDescent="0.3">
+    <row r="143" spans="2:156" x14ac:dyDescent="0.3">
       <c r="B143" t="s">
         <v>121</v>
       </c>
@@ -13047,7 +13528,7 @@
       <c r="Q143" s="5"/>
       <c r="R143" s="5"/>
     </row>
-    <row r="144" spans="2:38" x14ac:dyDescent="0.3">
+    <row r="144" spans="2:156" x14ac:dyDescent="0.3">
       <c r="B144" t="s">
         <v>105</v>
       </c>
@@ -13647,24 +14128,24 @@
         <v>122</v>
       </c>
       <c r="H172" s="5">
-        <f t="shared" ref="H172:M172" si="219">H143+SUM(H144:H171)</f>
+        <f t="shared" ref="H172:M172" si="222">H143+SUM(H144:H171)</f>
         <v>-624.9</v>
       </c>
       <c r="I172" s="5">
-        <f t="shared" si="219"/>
+        <f t="shared" si="222"/>
         <v>-863.89999999999986</v>
       </c>
       <c r="J172" s="5">
-        <f t="shared" si="219"/>
+        <f t="shared" si="222"/>
         <v>-1106.7000000000003</v>
       </c>
       <c r="K172" s="5"/>
       <c r="L172" s="5">
-        <f t="shared" si="219"/>
+        <f t="shared" si="222"/>
         <v>-422.19999999999993</v>
       </c>
       <c r="M172" s="5">
-        <f t="shared" si="219"/>
+        <f t="shared" si="222"/>
         <v>-597.09999999999991</v>
       </c>
       <c r="P172" s="5">
